--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="257" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="149">
   <si>
     <t>Mat</t>
   </si>
@@ -82,130 +82,226 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>OLMOS</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>BALTAZARES</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>DE LUNA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BRETON</t>
+    <t>ESPERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>TINOCO</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
   </si>
   <si>
     <t>CUATRA</t>
   </si>
   <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
     <t>MORALES</t>
   </si>
   <si>
     <t>OLTEHUA</t>
   </si>
   <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>CONTRERAS</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>CORDOVA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>CARRILLO</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>TZIZIHUA</t>
   </si>
   <si>
     <t>LEON</t>
   </si>
   <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
     <t>VELASCO</t>
   </si>
   <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>OLIVERA</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
   </si>
   <si>
     <t>ZOPIYACTLE</t>
@@ -214,40 +310,103 @@
     <t>SUAREZ</t>
   </si>
   <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
     <t>REYNOSO</t>
   </si>
   <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>CARRILLO</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>TZIZIHUA</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
+    <t>SAID ANDRES</t>
+  </si>
+  <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
+    <t>JOHAN ALEJANDRO</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>IVETTE</t>
+  </si>
+  <si>
+    <t>ELIAS ALONSO</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL ONAM</t>
+  </si>
+  <si>
+    <t>EUDY</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>ANGEL DAVID</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
   </si>
   <si>
     <t>LUIS ENRIQUE</t>
@@ -256,46 +415,43 @@
     <t>CRISTIAN JAHIR</t>
   </si>
   <si>
-    <t>SAID ANDRES</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
     <t>JORGE ALEJANDRO</t>
   </si>
   <si>
     <t>JONATHAN</t>
   </si>
   <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>JESUS HUMBERTO</t>
+  </si>
+  <si>
+    <t>ERNESTO</t>
+  </si>
+  <si>
+    <t>TANIA</t>
   </si>
   <si>
     <t>MARIA</t>
@@ -304,61 +460,10 @@
     <t>KIMBERLY ALONDRA</t>
   </si>
   <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
     <t>VALERIA</t>
   </si>
   <si>
     <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
-  </si>
-  <si>
-    <t>ANGEL DAVID</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>TANIA</t>
   </si>
 </sst>
 </file>
@@ -1283,7 +1388,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G39"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1315,16 +1420,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920080</v>
+        <v>19330051920051</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>77</v>
+        <v>98</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1338,16 +1443,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920081</v>
+        <v>20330051920082</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D3" t="s">
-        <v>78</v>
+        <v>99</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1361,16 +1466,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920082</v>
+        <v>20330051920091</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>61</v>
       </c>
       <c r="D4" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1384,16 +1489,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920091</v>
+        <v>20330051920093</v>
       </c>
       <c r="B5" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>62</v>
       </c>
       <c r="D5" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1407,22 +1512,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920064</v>
+        <v>20330051920202</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="D6" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1430,22 +1535,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920068</v>
+        <v>20330051920204</v>
       </c>
       <c r="B7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D7" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1453,16 +1558,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920202</v>
+        <v>20330051920213</v>
       </c>
       <c r="B8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D8" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1476,16 +1581,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920204</v>
+        <v>20330051920214</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D9" t="s">
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1499,22 +1604,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920213</v>
+        <v>20330051920260</v>
       </c>
       <c r="B10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="D10" t="s">
-        <v>85</v>
+        <v>106</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1522,22 +1627,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920214</v>
+        <v>20330051920270</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="D11" t="s">
-        <v>86</v>
+        <v>107</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1545,16 +1650,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920260</v>
+        <v>20330051920272</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="D12" t="s">
-        <v>87</v>
+        <v>108</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
@@ -1568,16 +1673,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920270</v>
+        <v>19220030050208</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="D13" t="s">
-        <v>88</v>
+        <v>109</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1591,16 +1696,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920272</v>
+        <v>20330051920278</v>
       </c>
       <c r="B14" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1614,22 +1719,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19220030050208</v>
+        <v>19330051920360</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C15" t="s">
-        <v>60</v>
+        <v>72</v>
       </c>
       <c r="D15" t="s">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1637,22 +1742,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920278</v>
+        <v>20330051920116</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C16" t="s">
-        <v>61</v>
+        <v>73</v>
       </c>
       <c r="D16" t="s">
-        <v>91</v>
+        <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G16">
         <v>2</v>
@@ -1660,16 +1765,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>19330051920360</v>
+        <v>20330051920123</v>
       </c>
       <c r="B17" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C17" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D17" t="s">
-        <v>92</v>
+        <v>113</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1683,16 +1788,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920121</v>
+        <v>20330051920125</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="D18" t="s">
-        <v>93</v>
+        <v>114</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1706,16 +1811,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920128</v>
+        <v>20330051920125</v>
       </c>
       <c r="B19" t="s">
+        <v>22</v>
+      </c>
+      <c r="C19" t="s">
         <v>30</v>
       </c>
-      <c r="C19" t="s">
-        <v>64</v>
-      </c>
       <c r="D19" t="s">
-        <v>94</v>
+        <v>114</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1729,16 +1834,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>19330051920383</v>
+        <v>20330051920127</v>
       </c>
       <c r="B20" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C20" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D20" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1752,16 +1857,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>19330051920383</v>
+        <v>20330051920127</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C21" t="s">
-        <v>65</v>
+        <v>30</v>
       </c>
       <c r="D21" t="s">
-        <v>95</v>
+        <v>115</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1775,19 +1880,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920139</v>
+        <v>20330051920131</v>
       </c>
       <c r="B22" t="s">
         <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -1798,16 +1903,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920387</v>
+        <v>20330051920131</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1821,19 +1926,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920399</v>
+        <v>20330051920134</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -1844,22 +1949,22 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920322</v>
+        <v>20330051920134</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C25" t="s">
-        <v>44</v>
+        <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G25">
         <v>2</v>
@@ -1867,22 +1972,22 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920325</v>
+        <v>20330051920137</v>
       </c>
       <c r="B26" t="s">
-        <v>30</v>
+        <v>39</v>
       </c>
       <c r="C26" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G26">
         <v>2</v>
@@ -1890,22 +1995,22 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920329</v>
+        <v>20330051920137</v>
       </c>
       <c r="B27" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C27" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G27">
         <v>2</v>
@@ -1913,22 +2018,22 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920335</v>
+        <v>19330051920383</v>
       </c>
       <c r="B28" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C28" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
       </c>
       <c r="F28" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28">
         <v>2</v>
@@ -1936,254 +2041,783 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920197</v>
+        <v>19330051920383</v>
       </c>
       <c r="B29" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C29" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>103</v>
+        <v>119</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G29">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920198</v>
+        <v>20330051920141</v>
       </c>
       <c r="B30" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C30" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>104</v>
+        <v>120</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
       </c>
       <c r="F30" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G30">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920199</v>
+        <v>20330051920141</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C31" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
       <c r="D31" t="s">
-        <v>105</v>
+        <v>120</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920201</v>
+        <v>20330051920389</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C32" t="s">
-        <v>21</v>
+        <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>106</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
         <v>8</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G32">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>19330051920290</v>
+        <v>20330051920389</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="C33" t="s">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="D33" t="s">
-        <v>107</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G33">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920210</v>
+        <v>20330051920144</v>
       </c>
       <c r="B34" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C34" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="D34" t="s">
-        <v>108</v>
+        <v>122</v>
       </c>
       <c r="E34" t="s">
         <v>8</v>
       </c>
       <c r="F34" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G34">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920215</v>
+        <v>20330051920387</v>
       </c>
       <c r="B35" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C35" t="s">
-        <v>30</v>
+        <v>81</v>
       </c>
       <c r="D35" t="s">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
         <v>8</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G35">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920217</v>
+        <v>20330051920387</v>
       </c>
       <c r="B36" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C36" t="s">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>110</v>
+        <v>123</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G36">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920268</v>
+        <v>20330051920148</v>
       </c>
       <c r="B37" t="s">
-        <v>21</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="D37" t="s">
-        <v>111</v>
+        <v>124</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G37">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920282</v>
+        <v>20330051920148</v>
       </c>
       <c r="B38" t="s">
-        <v>48</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>82</v>
       </c>
       <c r="D38" t="s">
-        <v>112</v>
+        <v>124</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G38">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
+        <v>19330051920399</v>
+      </c>
+      <c r="B39" t="s">
+        <v>45</v>
+      </c>
+      <c r="C39" t="s">
+        <v>83</v>
+      </c>
+      <c r="D39" t="s">
+        <v>125</v>
+      </c>
+      <c r="E39" t="s">
+        <v>9</v>
+      </c>
+      <c r="F39" t="s">
+        <v>13</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7">
+      <c r="A40">
+        <v>20330051920322</v>
+      </c>
+      <c r="B40" t="s">
+        <v>36</v>
+      </c>
+      <c r="C40" t="s">
+        <v>51</v>
+      </c>
+      <c r="D40" t="s">
+        <v>126</v>
+      </c>
+      <c r="E40" t="s">
+        <v>8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>14</v>
+      </c>
+      <c r="G40">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7">
+      <c r="A41">
+        <v>20330051920325</v>
+      </c>
+      <c r="B41" t="s">
+        <v>30</v>
+      </c>
+      <c r="C41" t="s">
+        <v>84</v>
+      </c>
+      <c r="D41" t="s">
+        <v>127</v>
+      </c>
+      <c r="E41" t="s">
+        <v>8</v>
+      </c>
+      <c r="F41" t="s">
+        <v>14</v>
+      </c>
+      <c r="G41">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7">
+      <c r="A42">
+        <v>20330051920329</v>
+      </c>
+      <c r="B42" t="s">
+        <v>46</v>
+      </c>
+      <c r="C42" t="s">
+        <v>85</v>
+      </c>
+      <c r="D42" t="s">
+        <v>128</v>
+      </c>
+      <c r="E42" t="s">
+        <v>8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>14</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43">
+        <v>20330051920335</v>
+      </c>
+      <c r="B43" t="s">
+        <v>47</v>
+      </c>
+      <c r="C43" t="s">
+        <v>86</v>
+      </c>
+      <c r="D43" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" t="s">
+        <v>8</v>
+      </c>
+      <c r="F43" t="s">
+        <v>14</v>
+      </c>
+      <c r="G43">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44">
+        <v>20330051920080</v>
+      </c>
+      <c r="B44" t="s">
+        <v>22</v>
+      </c>
+      <c r="C44" t="s">
+        <v>87</v>
+      </c>
+      <c r="D44" t="s">
+        <v>130</v>
+      </c>
+      <c r="E44" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" t="s">
+        <v>10</v>
+      </c>
+      <c r="G44">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45">
+        <v>20330051920081</v>
+      </c>
+      <c r="B45" t="s">
+        <v>22</v>
+      </c>
+      <c r="C45" t="s">
+        <v>40</v>
+      </c>
+      <c r="D45" t="s">
+        <v>131</v>
+      </c>
+      <c r="E45" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" t="s">
+        <v>10</v>
+      </c>
+      <c r="G45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46">
+        <v>20330051920064</v>
+      </c>
+      <c r="B46" t="s">
+        <v>48</v>
+      </c>
+      <c r="C46" t="s">
+        <v>88</v>
+      </c>
+      <c r="D46" t="s">
+        <v>132</v>
+      </c>
+      <c r="E46" t="s">
+        <v>8</v>
+      </c>
+      <c r="F46" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7">
+      <c r="A47">
+        <v>20330051920068</v>
+      </c>
+      <c r="B47" t="s">
+        <v>49</v>
+      </c>
+      <c r="C47" t="s">
+        <v>22</v>
+      </c>
+      <c r="D47" t="s">
+        <v>133</v>
+      </c>
+      <c r="E47" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" t="s">
+        <v>10</v>
+      </c>
+      <c r="G47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48">
+        <v>20330051920197</v>
+      </c>
+      <c r="B48" t="s">
+        <v>50</v>
+      </c>
+      <c r="C48" t="s">
+        <v>89</v>
+      </c>
+      <c r="D48" t="s">
+        <v>134</v>
+      </c>
+      <c r="E48" t="s">
+        <v>8</v>
+      </c>
+      <c r="F48" t="s">
+        <v>11</v>
+      </c>
+      <c r="G48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49">
+        <v>20330051920198</v>
+      </c>
+      <c r="B49" t="s">
+        <v>51</v>
+      </c>
+      <c r="C49" t="s">
+        <v>90</v>
+      </c>
+      <c r="D49" t="s">
+        <v>135</v>
+      </c>
+      <c r="E49" t="s">
+        <v>8</v>
+      </c>
+      <c r="F49" t="s">
+        <v>11</v>
+      </c>
+      <c r="G49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50">
+        <v>20330051920199</v>
+      </c>
+      <c r="B50" t="s">
+        <v>51</v>
+      </c>
+      <c r="C50" t="s">
+        <v>91</v>
+      </c>
+      <c r="D50" t="s">
+        <v>136</v>
+      </c>
+      <c r="E50" t="s">
+        <v>8</v>
+      </c>
+      <c r="F50" t="s">
+        <v>11</v>
+      </c>
+      <c r="G50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51">
+        <v>20330051920201</v>
+      </c>
+      <c r="B51" t="s">
+        <v>52</v>
+      </c>
+      <c r="C51" t="s">
+        <v>22</v>
+      </c>
+      <c r="D51" t="s">
+        <v>137</v>
+      </c>
+      <c r="E51" t="s">
+        <v>8</v>
+      </c>
+      <c r="F51" t="s">
+        <v>11</v>
+      </c>
+      <c r="G51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52">
+        <v>19330051920290</v>
+      </c>
+      <c r="B52" t="s">
+        <v>53</v>
+      </c>
+      <c r="C52" t="s">
+        <v>92</v>
+      </c>
+      <c r="D52" t="s">
+        <v>138</v>
+      </c>
+      <c r="E52" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>11</v>
+      </c>
+      <c r="G52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53">
+        <v>20330051920210</v>
+      </c>
+      <c r="B53" t="s">
+        <v>54</v>
+      </c>
+      <c r="C53" t="s">
+        <v>63</v>
+      </c>
+      <c r="D53" t="s">
+        <v>139</v>
+      </c>
+      <c r="E53" t="s">
+        <v>8</v>
+      </c>
+      <c r="F53" t="s">
+        <v>11</v>
+      </c>
+      <c r="G53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54">
+        <v>20330051920215</v>
+      </c>
+      <c r="B54" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" t="s">
+        <v>30</v>
+      </c>
+      <c r="D54" t="s">
+        <v>140</v>
+      </c>
+      <c r="E54" t="s">
+        <v>8</v>
+      </c>
+      <c r="F54" t="s">
+        <v>11</v>
+      </c>
+      <c r="G54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55">
+        <v>20330051920217</v>
+      </c>
+      <c r="B55" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" t="s">
+        <v>93</v>
+      </c>
+      <c r="D55" t="s">
+        <v>141</v>
+      </c>
+      <c r="E55" t="s">
+        <v>8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>11</v>
+      </c>
+      <c r="G55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56">
+        <v>20330051920268</v>
+      </c>
+      <c r="B56" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" t="s">
+        <v>51</v>
+      </c>
+      <c r="D56" t="s">
+        <v>142</v>
+      </c>
+      <c r="E56" t="s">
+        <v>8</v>
+      </c>
+      <c r="F56" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57">
+        <v>20330051920282</v>
+      </c>
+      <c r="B57" t="s">
+        <v>55</v>
+      </c>
+      <c r="C57" t="s">
+        <v>33</v>
+      </c>
+      <c r="D57" t="s">
+        <v>143</v>
+      </c>
+      <c r="E57" t="s">
+        <v>8</v>
+      </c>
+      <c r="F57" t="s">
+        <v>12</v>
+      </c>
+      <c r="G57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7">
+      <c r="A58">
         <v>18330051920393</v>
       </c>
-      <c r="B39" t="s">
-        <v>49</v>
-      </c>
-      <c r="C39" t="s">
-        <v>76</v>
-      </c>
-      <c r="D39" t="s">
-        <v>113</v>
-      </c>
-      <c r="E39" t="s">
-        <v>8</v>
-      </c>
-      <c r="F39" t="s">
-        <v>13</v>
-      </c>
-      <c r="G39">
+      <c r="B58" t="s">
+        <v>56</v>
+      </c>
+      <c r="C58" t="s">
+        <v>94</v>
+      </c>
+      <c r="D58" t="s">
+        <v>144</v>
+      </c>
+      <c r="E58" t="s">
+        <v>8</v>
+      </c>
+      <c r="F58" t="s">
+        <v>13</v>
+      </c>
+      <c r="G58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7">
+      <c r="A59">
+        <v>20330051920121</v>
+      </c>
+      <c r="B59" t="s">
+        <v>57</v>
+      </c>
+      <c r="C59" t="s">
+        <v>95</v>
+      </c>
+      <c r="D59" t="s">
+        <v>145</v>
+      </c>
+      <c r="E59" t="s">
+        <v>8</v>
+      </c>
+      <c r="F59" t="s">
+        <v>13</v>
+      </c>
+      <c r="G59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7">
+      <c r="A60">
+        <v>20330051920128</v>
+      </c>
+      <c r="B60" t="s">
+        <v>30</v>
+      </c>
+      <c r="C60" t="s">
+        <v>96</v>
+      </c>
+      <c r="D60" t="s">
+        <v>146</v>
+      </c>
+      <c r="E60" t="s">
+        <v>9</v>
+      </c>
+      <c r="F60" t="s">
+        <v>13</v>
+      </c>
+      <c r="G60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7">
+      <c r="A61">
+        <v>20330051920139</v>
+      </c>
+      <c r="B61" t="s">
+        <v>58</v>
+      </c>
+      <c r="C61" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61" t="s">
+        <v>147</v>
+      </c>
+      <c r="E61" t="s">
+        <v>9</v>
+      </c>
+      <c r="F61" t="s">
+        <v>13</v>
+      </c>
+      <c r="G61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7">
+      <c r="A62">
+        <v>19330051920387</v>
+      </c>
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" t="s">
+        <v>148</v>
+      </c>
+      <c r="E62" t="s">
+        <v>9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>13</v>
+      </c>
+      <c r="G62">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="372" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="153">
   <si>
     <t>Mat</t>
   </si>
@@ -82,186 +82,183 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>DE LA CRUZ</t>
-  </si>
-  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
-    <t>OLMOS</t>
-  </si>
-  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ESPERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>DE JESUS</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>BALTAZARES</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>DE LUNA</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
   </si>
   <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>TINOCO</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
+    <t>ALAMILLO</t>
+  </si>
+  <si>
+    <t>CASTILLO</t>
+  </si>
+  <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>ZACARIAS</t>
+  </si>
+  <si>
+    <t>HUERTA</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
   </si>
   <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>ALAMILLO</t>
-  </si>
-  <si>
-    <t>CASTILLO</t>
-  </si>
-  <si>
-    <t>OLIVERA</t>
-  </si>
-  <si>
-    <t>ZACARIAS</t>
-  </si>
-  <si>
-    <t>HUERTA</t>
-  </si>
-  <si>
-    <t>CONTRERAS</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>CORDOVA</t>
-  </si>
-  <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
     <t>SALAZAR</t>
   </si>
   <si>
@@ -271,130 +268,202 @@
     <t>VERGEL</t>
   </si>
   <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>JESUS ISRAEL</t>
-  </si>
-  <si>
     <t>SAID ANDRES</t>
   </si>
   <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
     <t>JOHAN ALEJANDRO</t>
   </si>
   <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>SUSANA</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>MARCO JOSAFAT</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
     <t>ITZEL</t>
   </si>
   <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>SUSANA</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>IVETTE</t>
-  </si>
-  <si>
-    <t>ELIAS ALONSO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL ONAM</t>
-  </si>
-  <si>
-    <t>EUDY</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>TANIA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
   </si>
   <si>
     <t>MARCOS</t>
@@ -403,67 +472,10 @@
     <t>ANGEL DAVID</t>
   </si>
   <si>
-    <t>JUAN GUILLERMO</t>
+    <t>MICHELLE ROBERTA</t>
   </si>
   <si>
     <t>DORA LUZ</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>JESUS HUMBERTO</t>
-  </si>
-  <si>
-    <t>ERNESTO</t>
-  </si>
-  <si>
-    <t>TANIA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
   </si>
 </sst>
 </file>
@@ -916,19 +928,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>6</v>
       </c>
       <c r="F4">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="G4">
-        <v>47.37</v>
+        <v>68.42</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>6.8</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1105,16 +1117,19 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>19</v>
+        <v>1</v>
       </c>
       <c r="E4">
+        <v>4</v>
+      </c>
+      <c r="F4">
         <v>15</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H4">
+        <v>6.9</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1288,19 +1303,19 @@
         <v>19</v>
       </c>
       <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
         <v>4</v>
       </c>
-      <c r="E4">
-        <v>6</v>
-      </c>
       <c r="F4">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="G4">
-        <v>47.37</v>
+        <v>78.95</v>
       </c>
       <c r="H4">
-        <v>7</v>
+        <v>7.3</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1388,7 +1403,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G65"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1420,16 +1435,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>19330051920051</v>
+        <v>20330051920082</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="D2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1443,16 +1458,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920082</v>
+        <v>20330051920093</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="D3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1466,22 +1481,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920091</v>
+        <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1489,22 +1504,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920093</v>
+        <v>20330051920193</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1512,16 +1527,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920202</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1535,16 +1550,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920204</v>
+        <v>20330051920213</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="D7" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1558,16 +1573,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920213</v>
+        <v>20330051920214</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1581,16 +1596,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920214</v>
+        <v>20330051920218</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D9" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1604,16 +1619,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920260</v>
+        <v>20330051920278</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D10" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1627,22 +1642,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920270</v>
+        <v>19330051920360</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1650,22 +1665,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920272</v>
+        <v>20330051920116</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C12" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D12" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1673,22 +1688,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19220030050208</v>
+        <v>20330051920123</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="D13" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1696,22 +1711,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920278</v>
+        <v>20330051920125</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>71</v>
+        <v>32</v>
       </c>
       <c r="D14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1719,13 +1734,13 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920360</v>
+        <v>20330051920125</v>
       </c>
       <c r="B15" t="s">
-        <v>34</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>72</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
         <v>111</v>
@@ -1742,19 +1757,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920116</v>
+        <v>20330051920127</v>
       </c>
       <c r="B16" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>73</v>
+        <v>32</v>
       </c>
       <c r="D16" t="s">
         <v>112</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
@@ -1765,16 +1780,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920123</v>
+        <v>20330051920127</v>
       </c>
       <c r="B17" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C17" t="s">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="D17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E17" t="s">
         <v>9</v>
@@ -1788,16 +1803,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920125</v>
+        <v>20330051920131</v>
       </c>
       <c r="B18" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C18" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D18" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1811,16 +1826,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920125</v>
+        <v>20330051920131</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>30</v>
+        <v>73</v>
       </c>
       <c r="D19" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E19" t="s">
         <v>9</v>
@@ -1834,16 +1849,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920127</v>
+        <v>20330051920134</v>
       </c>
       <c r="B20" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1857,16 +1872,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920127</v>
+        <v>20330051920134</v>
       </c>
       <c r="B21" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>30</v>
+        <v>74</v>
       </c>
       <c r="D21" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="E21" t="s">
         <v>9</v>
@@ -1880,16 +1895,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920131</v>
+        <v>20330051920137</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
         <v>75</v>
       </c>
       <c r="D22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1903,16 +1918,16 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920131</v>
+        <v>20330051920137</v>
       </c>
       <c r="B23" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C23" t="s">
         <v>75</v>
       </c>
       <c r="D23" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1926,16 +1941,16 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920134</v>
+        <v>19330051920383</v>
       </c>
       <c r="B24" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
         <v>76</v>
       </c>
       <c r="D24" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E24" t="s">
         <v>8</v>
@@ -1949,16 +1964,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920134</v>
+        <v>19330051920383</v>
       </c>
       <c r="B25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C25" t="s">
         <v>76</v>
       </c>
       <c r="D25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E25" t="s">
         <v>9</v>
@@ -1972,16 +1987,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920137</v>
+        <v>20330051920141</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
         <v>77</v>
       </c>
       <c r="D26" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1995,16 +2010,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920137</v>
+        <v>20330051920141</v>
       </c>
       <c r="B27" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C27" t="s">
         <v>77</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="E27" t="s">
         <v>9</v>
@@ -2018,16 +2033,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>19330051920383</v>
+        <v>20330051920389</v>
       </c>
       <c r="B28" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
         <v>78</v>
       </c>
       <c r="D28" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -2041,16 +2056,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>19330051920383</v>
+        <v>20330051920389</v>
       </c>
       <c r="B29" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C29" t="s">
         <v>78</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E29" t="s">
         <v>9</v>
@@ -2064,16 +2079,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920141</v>
+        <v>20330051920144</v>
       </c>
       <c r="B30" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
         <v>79</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -2087,19 +2102,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920141</v>
+        <v>20330051920387</v>
       </c>
       <c r="B31" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D31" t="s">
         <v>120</v>
       </c>
       <c r="E31" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -2110,19 +2125,19 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920389</v>
+        <v>20330051920387</v>
       </c>
       <c r="B32" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
         <v>80</v>
       </c>
       <c r="D32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E32" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -2133,19 +2148,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920389</v>
+        <v>20330051920148</v>
       </c>
       <c r="B33" t="s">
-        <v>42</v>
+        <v>27</v>
       </c>
       <c r="C33" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D33" t="s">
         <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -2156,19 +2171,19 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920144</v>
+        <v>20330051920148</v>
       </c>
       <c r="B34" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
       <c r="C34" t="s">
-        <v>61</v>
+        <v>81</v>
       </c>
       <c r="D34" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E34" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -2179,19 +2194,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920387</v>
+        <v>19330051920399</v>
       </c>
       <c r="B35" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -2202,22 +2217,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920387</v>
+        <v>20330051920317</v>
       </c>
       <c r="B36" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="D36" t="s">
         <v>123</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2225,13 +2240,13 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920148</v>
+        <v>20330051920397</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>43</v>
       </c>
       <c r="C37" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D37" t="s">
         <v>124</v>
@@ -2240,7 +2255,7 @@
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2248,22 +2263,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920148</v>
+        <v>20330051920326</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>44</v>
       </c>
       <c r="C38" t="s">
-        <v>82</v>
+        <v>60</v>
       </c>
       <c r="D38" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -2271,22 +2286,22 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>19330051920399</v>
+        <v>20330051920329</v>
       </c>
       <c r="B39" t="s">
         <v>45</v>
       </c>
       <c r="C39" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D39" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E39" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -2294,16 +2309,16 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>20330051920322</v>
+        <v>20330051920330</v>
       </c>
       <c r="B40" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="C40" t="s">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="D40" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E40" t="s">
         <v>8</v>
@@ -2317,85 +2332,85 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>20330051920325</v>
+        <v>20330051920071</v>
       </c>
       <c r="B41" t="s">
-        <v>30</v>
+        <v>47</v>
       </c>
       <c r="C41" t="s">
-        <v>84</v>
+        <v>53</v>
       </c>
       <c r="D41" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E41" t="s">
         <v>8</v>
       </c>
       <c r="F41" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G41">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>20330051920329</v>
+        <v>20330051920080</v>
       </c>
       <c r="B42" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="C42" t="s">
         <v>85</v>
       </c>
       <c r="D42" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E42" t="s">
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>20330051920335</v>
+        <v>20330051920081</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>36</v>
       </c>
       <c r="D43" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G43">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>20330051920080</v>
+        <v>20330051920087</v>
       </c>
       <c r="B44" t="s">
-        <v>22</v>
+        <v>48</v>
       </c>
       <c r="C44" t="s">
-        <v>87</v>
+        <v>32</v>
       </c>
       <c r="D44" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2409,16 +2424,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>20330051920081</v>
+        <v>20330051920064</v>
       </c>
       <c r="B45" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
       <c r="C45" t="s">
-        <v>40</v>
+        <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2432,16 +2447,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>20330051920064</v>
+        <v>20330051920068</v>
       </c>
       <c r="B46" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C46" t="s">
-        <v>88</v>
+        <v>21</v>
       </c>
       <c r="D46" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2455,22 +2470,22 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>20330051920068</v>
+        <v>20330051920191</v>
       </c>
       <c r="B47" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C47" t="s">
-        <v>22</v>
+        <v>87</v>
       </c>
       <c r="D47" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2481,13 +2496,13 @@
         <v>20330051920197</v>
       </c>
       <c r="B48" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C48" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D48" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2504,13 +2519,13 @@
         <v>20330051920198</v>
       </c>
       <c r="B49" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D49" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2527,13 +2542,13 @@
         <v>20330051920199</v>
       </c>
       <c r="B50" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C50" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D50" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2550,13 +2565,13 @@
         <v>20330051920201</v>
       </c>
       <c r="B51" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C51" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D51" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2570,16 +2585,16 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>19330051920290</v>
+        <v>20330051920202</v>
       </c>
       <c r="B52" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C52" t="s">
-        <v>92</v>
+        <v>64</v>
       </c>
       <c r="D52" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
@@ -2593,16 +2608,16 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>20330051920210</v>
+        <v>19330051920290</v>
       </c>
       <c r="B53" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C53" t="s">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
@@ -2616,16 +2631,16 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>20330051920215</v>
+        <v>20330051920210</v>
       </c>
       <c r="B54" t="s">
-        <v>28</v>
+        <v>57</v>
       </c>
       <c r="C54" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="D54" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
@@ -2639,16 +2654,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>20330051920217</v>
+        <v>20330051920215</v>
       </c>
       <c r="B55" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C55" t="s">
-        <v>93</v>
+        <v>32</v>
       </c>
       <c r="D55" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2662,22 +2677,22 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>20330051920268</v>
+        <v>20330051920217</v>
       </c>
       <c r="B56" t="s">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="C56" t="s">
-        <v>51</v>
+        <v>92</v>
       </c>
       <c r="D56" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
       </c>
       <c r="F56" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2685,22 +2700,22 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>20330051920282</v>
+        <v>18330051920393</v>
       </c>
       <c r="B57" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="C57" t="s">
-        <v>33</v>
+        <v>93</v>
       </c>
       <c r="D57" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2708,16 +2723,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>18330051920393</v>
+        <v>20330051920121</v>
       </c>
       <c r="B58" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C58" t="s">
         <v>94</v>
       </c>
       <c r="D58" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2731,19 +2746,19 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>20330051920121</v>
+        <v>20330051920128</v>
       </c>
       <c r="B59" t="s">
-        <v>57</v>
+        <v>32</v>
       </c>
       <c r="C59" t="s">
         <v>95</v>
       </c>
       <c r="D59" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E59" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F59" t="s">
         <v>13</v>
@@ -2754,16 +2769,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>20330051920128</v>
+        <v>20330051920139</v>
       </c>
       <c r="B60" t="s">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C60" t="s">
         <v>96</v>
       </c>
       <c r="D60" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E60" t="s">
         <v>9</v>
@@ -2777,16 +2792,16 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>20330051920139</v>
+        <v>19330051920387</v>
       </c>
       <c r="B61" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C61" t="s">
-        <v>97</v>
+        <v>31</v>
       </c>
       <c r="D61" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E61" t="s">
         <v>9</v>
@@ -2800,24 +2815,93 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>19330051920387</v>
+        <v>20330051920322</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C62" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="D62" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E62" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7">
+      <c r="A63">
+        <v>20330051920325</v>
+      </c>
+      <c r="B63" t="s">
+        <v>32</v>
+      </c>
+      <c r="C63" t="s">
+        <v>97</v>
+      </c>
+      <c r="D63" t="s">
+        <v>150</v>
+      </c>
+      <c r="E63" t="s">
+        <v>8</v>
+      </c>
+      <c r="F63" t="s">
+        <v>14</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7">
+      <c r="A64">
+        <v>20330051920331</v>
+      </c>
+      <c r="B64" t="s">
+        <v>26</v>
+      </c>
+      <c r="C64" t="s">
+        <v>64</v>
+      </c>
+      <c r="D64" t="s">
+        <v>151</v>
+      </c>
+      <c r="E64" t="s">
+        <v>8</v>
+      </c>
+      <c r="F64" t="s">
+        <v>14</v>
+      </c>
+      <c r="G64">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7">
+      <c r="A65">
+        <v>20330051920335</v>
+      </c>
+      <c r="B65" t="s">
+        <v>62</v>
+      </c>
+      <c r="C65" t="s">
+        <v>98</v>
+      </c>
+      <c r="D65" t="s">
+        <v>152</v>
+      </c>
+      <c r="E65" t="s">
+        <v>8</v>
+      </c>
+      <c r="F65" t="s">
+        <v>14</v>
+      </c>
+      <c r="G65">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="158">
   <si>
     <t>Mat</t>
   </si>
@@ -85,6 +85,9 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
@@ -130,81 +133,84 @@
     <t>MENDEZ</t>
   </si>
   <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
     <t>OSORIO</t>
   </si>
   <si>
     <t>PACHECO</t>
   </si>
   <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>ZARATE</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>OCAÑA</t>
+  </si>
+  <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>ESPERON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>ROBLES</t>
+  </si>
+  <si>
+    <t>BAUTISTA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
     <t>DE LA ROSA</t>
   </si>
   <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>OCAÑA</t>
-  </si>
-  <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>TEXCAHUA</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>ESPERON</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GOMEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>ROBLES</t>
-  </si>
-  <si>
-    <t>BAUTISTA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
@@ -238,6 +244,9 @@
     <t>JUAREZ</t>
   </si>
   <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
     <t>BASILIO</t>
   </si>
   <si>
@@ -250,66 +259,69 @@
     <t>SANTOS</t>
   </si>
   <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
     <t>MACHORRO</t>
   </si>
   <si>
     <t>MAZAHUA</t>
   </si>
   <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>VERGEL</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>MONTALVO</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>VELASCO</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>MORA</t>
+  </si>
+  <si>
+    <t>ROQUE</t>
+  </si>
+  <si>
+    <t>VILLEGAS</t>
+  </si>
+  <si>
+    <t>SARMIENTO</t>
+  </si>
+  <si>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>MARCELINO</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>VERGEL</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>MONTALVO</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>VELASCO</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>MORA</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>VILLEGAS</t>
-  </si>
-  <si>
-    <t>SARMIENTO</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>MARCELINO</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
     <t>CARRILLO</t>
   </si>
   <si>
@@ -319,6 +331,9 @@
     <t>SAID ANDRES</t>
   </si>
   <si>
+    <t>GABRIEL JOSUE</t>
+  </si>
+  <si>
     <t>JOHAN ALEJANDRO</t>
   </si>
   <si>
@@ -352,6 +367,9 @@
     <t>EMELIN JIROMI</t>
   </si>
   <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
     <t>AIDA</t>
   </si>
   <si>
@@ -370,100 +388,97 @@
     <t>FATIMA</t>
   </si>
   <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
     <t>KARLA</t>
   </si>
   <si>
     <t>TAILY</t>
   </si>
   <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>KIMBERLY</t>
+  </si>
+  <si>
+    <t>PAULINA</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>EMMANUEL</t>
+  </si>
+  <si>
+    <t>JESUS ANTONIO</t>
+  </si>
+  <si>
+    <t>JUAN GUILLERMO</t>
+  </si>
+  <si>
+    <t>OZIEL</t>
+  </si>
+  <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
+    <t>CRISTIAN JAHIR</t>
+  </si>
+  <si>
+    <t>JORGE ALEJANDRO</t>
+  </si>
+  <si>
+    <t>JONATHAN</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>MIA VALENTINA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>FRIDA SOFIA</t>
+  </si>
+  <si>
+    <t>YAMILET</t>
+  </si>
+  <si>
+    <t>HEIDY MARIAM</t>
+  </si>
+  <si>
+    <t>JULIO CESAR</t>
+  </si>
+  <si>
+    <t>AMADA ARELY</t>
+  </si>
+  <si>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>TANIA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
     <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>PAULINA</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>EMMANUEL</t>
-  </si>
-  <si>
-    <t>JESUS ANTONIO</t>
-  </si>
-  <si>
-    <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>OZIEL</t>
-  </si>
-  <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
-  </si>
-  <si>
-    <t>CRISTIAN JAHIR</t>
-  </si>
-  <si>
-    <t>GABRIEL JOSUE</t>
-  </si>
-  <si>
-    <t>JORGE ALEJANDRO</t>
-  </si>
-  <si>
-    <t>JONATHAN</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>MIA VALENTINA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>FRIDA SOFIA</t>
-  </si>
-  <si>
-    <t>YAMILET</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>HEIDY MARIAM</t>
-  </si>
-  <si>
-    <t>JULIO CESAR</t>
-  </si>
-  <si>
-    <t>AMADA ARELY</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>TANIA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
   </si>
   <si>
     <t>MARCOS</t>
@@ -1403,7 +1418,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1441,10 +1456,10 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D2" t="s">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1458,16 +1473,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920093</v>
+        <v>20330051920087</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D3" t="s">
-        <v>100</v>
+        <v>104</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1481,22 +1496,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920190</v>
+        <v>20330051920093</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>101</v>
+        <v>105</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1504,16 +1519,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920193</v>
+        <v>20330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1527,16 +1542,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920196</v>
+        <v>20330051920193</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
-        <v>103</v>
+        <v>107</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1550,16 +1565,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920213</v>
+        <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>104</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1573,16 +1588,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920214</v>
+        <v>20330051920213</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D8" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1596,16 +1611,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920218</v>
+        <v>20330051920214</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D9" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1619,22 +1634,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920278</v>
+        <v>20330051920218</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D10" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1642,22 +1657,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920360</v>
+        <v>20330051920278</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1665,16 +1680,16 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920116</v>
+        <v>19330051920360</v>
       </c>
       <c r="B12" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D12" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="E12" t="s">
         <v>9</v>
@@ -1688,16 +1703,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920123</v>
+        <v>20330051920116</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>25</v>
       </c>
       <c r="C13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D13" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1711,19 +1726,19 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920125</v>
+        <v>20330051920123</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>74</v>
       </c>
       <c r="D14" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
         <v>13</v>
@@ -1734,19 +1749,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920125</v>
+        <v>20330051920124</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="D15" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -1757,19 +1772,19 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920127</v>
+        <v>20330051920124</v>
       </c>
       <c r="B16" t="s">
         <v>32</v>
       </c>
       <c r="C16" t="s">
-        <v>32</v>
+        <v>75</v>
       </c>
       <c r="D16" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="E16" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
@@ -1780,19 +1795,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920127</v>
+        <v>20330051920125</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="E17" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -1803,19 +1818,19 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920131</v>
+        <v>20330051920125</v>
       </c>
       <c r="B18" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" t="s">
         <v>33</v>
       </c>
-      <c r="C18" t="s">
-        <v>73</v>
-      </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="E18" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -1826,19 +1841,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920131</v>
+        <v>20330051920127</v>
       </c>
       <c r="B19" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>73</v>
+        <v>33</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="E19" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
@@ -1849,19 +1864,19 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920134</v>
+        <v>20330051920127</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>74</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="E20" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
@@ -1872,19 +1887,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920134</v>
+        <v>20330051920131</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D21" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="E21" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -1895,19 +1910,19 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920137</v>
+        <v>20330051920131</v>
       </c>
       <c r="B22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C22" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D22" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="E22" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -1918,19 +1933,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920137</v>
+        <v>20330051920134</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D23" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -1941,19 +1956,19 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920383</v>
+        <v>20330051920134</v>
       </c>
       <c r="B24" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C24" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D24" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -1964,19 +1979,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>19330051920383</v>
+        <v>20330051920137</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D25" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="E25" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -1987,19 +2002,19 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920141</v>
+        <v>20330051920137</v>
       </c>
       <c r="B26" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C26" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D26" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="E26" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -2010,19 +2025,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920141</v>
+        <v>19330051920383</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D27" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="E27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -2033,19 +2048,19 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920389</v>
+        <v>19330051920383</v>
       </c>
       <c r="B28" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C28" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="D28" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="E28" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -2056,19 +2071,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920389</v>
+        <v>20330051920140</v>
       </c>
       <c r="B29" t="s">
         <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D29" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="E29" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -2079,19 +2094,19 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920144</v>
+        <v>20330051920140</v>
       </c>
       <c r="B30" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C30" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D30" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="E30" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -2102,16 +2117,16 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920387</v>
+        <v>20330051920141</v>
       </c>
       <c r="B31" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D31" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E31" t="s">
         <v>8</v>
@@ -2125,16 +2140,16 @@
     </row>
     <row r="32" spans="1:7">
       <c r="A32">
-        <v>20330051920387</v>
+        <v>20330051920141</v>
       </c>
       <c r="B32" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C32" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="E32" t="s">
         <v>9</v>
@@ -2148,16 +2163,16 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920148</v>
+        <v>20330051920389</v>
       </c>
       <c r="B33" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D33" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E33" t="s">
         <v>8</v>
@@ -2171,16 +2186,16 @@
     </row>
     <row r="34" spans="1:7">
       <c r="A34">
-        <v>20330051920148</v>
+        <v>20330051920389</v>
       </c>
       <c r="B34" t="s">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="C34" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D34" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="E34" t="s">
         <v>9</v>
@@ -2194,19 +2209,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>19330051920399</v>
+        <v>20330051920387</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="D35" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E35" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -2217,22 +2232,22 @@
     </row>
     <row r="36" spans="1:7">
       <c r="A36">
-        <v>20330051920317</v>
+        <v>20330051920387</v>
       </c>
       <c r="B36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C36" t="s">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="D36" t="s">
         <v>123</v>
       </c>
       <c r="E36" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G36">
         <v>2</v>
@@ -2240,22 +2255,22 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920397</v>
+        <v>20330051920148</v>
       </c>
       <c r="B37" t="s">
-        <v>43</v>
+        <v>28</v>
       </c>
       <c r="C37" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="D37" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E37" t="s">
         <v>8</v>
       </c>
       <c r="F37" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G37">
         <v>2</v>
@@ -2263,22 +2278,22 @@
     </row>
     <row r="38" spans="1:7">
       <c r="A38">
-        <v>20330051920326</v>
+        <v>20330051920148</v>
       </c>
       <c r="B38" t="s">
-        <v>44</v>
+        <v>28</v>
       </c>
       <c r="C38" t="s">
-        <v>60</v>
+        <v>84</v>
       </c>
       <c r="D38" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E38" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F38" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G38">
         <v>2</v>
@@ -2286,22 +2301,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920329</v>
+        <v>20330051920153</v>
       </c>
       <c r="B39" t="s">
-        <v>45</v>
-      </c>
-      <c r="C39" t="s">
-        <v>84</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E39" t="s">
         <v>8</v>
       </c>
       <c r="F39" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G39">
         <v>2</v>
@@ -2309,22 +2321,19 @@
     </row>
     <row r="40" spans="1:7">
       <c r="A40">
-        <v>20330051920330</v>
+        <v>20330051920153</v>
       </c>
       <c r="B40" t="s">
-        <v>46</v>
-      </c>
-      <c r="C40" t="s">
-        <v>68</v>
+        <v>42</v>
       </c>
       <c r="D40" t="s">
         <v>127</v>
       </c>
       <c r="E40" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G40">
         <v>2</v>
@@ -2332,36 +2341,36 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>20330051920071</v>
+        <v>19330051920399</v>
       </c>
       <c r="B41" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C41" t="s">
-        <v>53</v>
+        <v>85</v>
       </c>
       <c r="D41" t="s">
         <v>128</v>
       </c>
       <c r="E41" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F41" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G41">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>20330051920080</v>
+        <v>20330051920317</v>
       </c>
       <c r="B42" t="s">
-        <v>21</v>
+        <v>44</v>
       </c>
       <c r="C42" t="s">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D42" t="s">
         <v>129</v>
@@ -2370,21 +2379,21 @@
         <v>8</v>
       </c>
       <c r="F42" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G42">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>20330051920081</v>
+        <v>20330051920397</v>
       </c>
       <c r="B43" t="s">
-        <v>21</v>
+        <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>36</v>
+        <v>86</v>
       </c>
       <c r="D43" t="s">
         <v>130</v>
@@ -2393,21 +2402,21 @@
         <v>8</v>
       </c>
       <c r="F43" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G43">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>20330051920087</v>
+        <v>20330051920326</v>
       </c>
       <c r="B44" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C44" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="D44" t="s">
         <v>131</v>
@@ -2416,21 +2425,21 @@
         <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G44">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>20330051920064</v>
+        <v>20330051920329</v>
       </c>
       <c r="B45" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C45" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D45" t="s">
         <v>132</v>
@@ -2439,21 +2448,21 @@
         <v>8</v>
       </c>
       <c r="F45" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>20330051920068</v>
+        <v>20330051920330</v>
       </c>
       <c r="B46" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>21</v>
+        <v>70</v>
       </c>
       <c r="D46" t="s">
         <v>133</v>
@@ -2462,21 +2471,21 @@
         <v>8</v>
       </c>
       <c r="F46" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G46">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>20330051920191</v>
+        <v>20330051920071</v>
       </c>
       <c r="B47" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>87</v>
+        <v>54</v>
       </c>
       <c r="D47" t="s">
         <v>134</v>
@@ -2485,7 +2494,7 @@
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G47">
         <v>1</v>
@@ -2493,10 +2502,10 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>20330051920197</v>
+        <v>20330051920080</v>
       </c>
       <c r="B48" t="s">
-        <v>52</v>
+        <v>21</v>
       </c>
       <c r="C48" t="s">
         <v>88</v>
@@ -2508,7 +2517,7 @@
         <v>8</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -2516,13 +2525,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>20330051920198</v>
+        <v>20330051920081</v>
       </c>
       <c r="B49" t="s">
-        <v>53</v>
+        <v>21</v>
       </c>
       <c r="C49" t="s">
-        <v>89</v>
+        <v>37</v>
       </c>
       <c r="D49" t="s">
         <v>136</v>
@@ -2531,7 +2540,7 @@
         <v>8</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -2539,13 +2548,13 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>20330051920199</v>
+        <v>20330051920064</v>
       </c>
       <c r="B50" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C50" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D50" t="s">
         <v>137</v>
@@ -2554,7 +2563,7 @@
         <v>8</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -2562,10 +2571,10 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>20330051920201</v>
+        <v>20330051920068</v>
       </c>
       <c r="B51" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="C51" t="s">
         <v>21</v>
@@ -2577,7 +2586,7 @@
         <v>8</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G51">
         <v>1</v>
@@ -2585,13 +2594,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>20330051920202</v>
+        <v>20330051920191</v>
       </c>
       <c r="B52" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>64</v>
+        <v>90</v>
       </c>
       <c r="D52" t="s">
         <v>139</v>
@@ -2608,10 +2617,10 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>19330051920290</v>
+        <v>20330051920197</v>
       </c>
       <c r="B53" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="C53" t="s">
         <v>91</v>
@@ -2631,13 +2640,13 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>20330051920210</v>
+        <v>20330051920198</v>
       </c>
       <c r="B54" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>64</v>
+        <v>92</v>
       </c>
       <c r="D54" t="s">
         <v>141</v>
@@ -2654,13 +2663,13 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>20330051920215</v>
+        <v>20330051920199</v>
       </c>
       <c r="B55" t="s">
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="C55" t="s">
-        <v>32</v>
+        <v>93</v>
       </c>
       <c r="D55" t="s">
         <v>142</v>
@@ -2677,13 +2686,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>20330051920217</v>
+        <v>20330051920201</v>
       </c>
       <c r="B56" t="s">
-        <v>27</v>
+        <v>55</v>
       </c>
       <c r="C56" t="s">
-        <v>92</v>
+        <v>21</v>
       </c>
       <c r="D56" t="s">
         <v>143</v>
@@ -2700,22 +2709,22 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>18330051920393</v>
+        <v>20330051920202</v>
       </c>
       <c r="B57" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="C57" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="D57" t="s">
-        <v>144</v>
+        <v>116</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
       </c>
       <c r="F57" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2723,22 +2732,22 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>20330051920121</v>
+        <v>19330051920290</v>
       </c>
       <c r="B58" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="C58" t="s">
         <v>94</v>
       </c>
       <c r="D58" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
       </c>
       <c r="F58" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2746,22 +2755,22 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>20330051920128</v>
+        <v>20330051920210</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>58</v>
       </c>
       <c r="C59" t="s">
-        <v>95</v>
+        <v>66</v>
       </c>
       <c r="D59" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E59" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F59" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2769,22 +2778,22 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>20330051920139</v>
+        <v>20330051920215</v>
       </c>
       <c r="B60" t="s">
-        <v>60</v>
+        <v>28</v>
       </c>
       <c r="C60" t="s">
-        <v>96</v>
+        <v>33</v>
       </c>
       <c r="D60" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E60" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F60" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -2792,22 +2801,22 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>19330051920387</v>
+        <v>20330051920217</v>
       </c>
       <c r="B61" t="s">
-        <v>61</v>
+        <v>28</v>
       </c>
       <c r="C61" t="s">
-        <v>31</v>
+        <v>95</v>
       </c>
       <c r="D61" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E61" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F61" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2815,22 +2824,22 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>20330051920322</v>
+        <v>18330051920393</v>
       </c>
       <c r="B62" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C62" t="s">
-        <v>53</v>
+        <v>96</v>
       </c>
       <c r="D62" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2838,22 +2847,22 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>20330051920325</v>
+        <v>20330051920121</v>
       </c>
       <c r="B63" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C63" t="s">
         <v>97</v>
       </c>
       <c r="D63" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2861,22 +2870,22 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>20330051920331</v>
+        <v>20330051920128</v>
       </c>
       <c r="B64" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C64" t="s">
-        <v>64</v>
+        <v>98</v>
       </c>
       <c r="D64" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="E64" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -2884,24 +2893,162 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
+        <v>20330051920139</v>
+      </c>
+      <c r="B65" t="s">
+        <v>61</v>
+      </c>
+      <c r="C65" t="s">
+        <v>99</v>
+      </c>
+      <c r="D65" t="s">
+        <v>151</v>
+      </c>
+      <c r="E65" t="s">
+        <v>9</v>
+      </c>
+      <c r="F65" t="s">
+        <v>13</v>
+      </c>
+      <c r="G65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7">
+      <c r="A66">
+        <v>19330051920387</v>
+      </c>
+      <c r="B66" t="s">
+        <v>62</v>
+      </c>
+      <c r="C66" t="s">
+        <v>32</v>
+      </c>
+      <c r="D66" t="s">
+        <v>152</v>
+      </c>
+      <c r="E66" t="s">
+        <v>9</v>
+      </c>
+      <c r="F66" t="s">
+        <v>13</v>
+      </c>
+      <c r="G66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7">
+      <c r="A67">
+        <v>20330051920144</v>
+      </c>
+      <c r="B67" t="s">
+        <v>63</v>
+      </c>
+      <c r="C67" t="s">
+        <v>100</v>
+      </c>
+      <c r="D67" t="s">
+        <v>153</v>
+      </c>
+      <c r="E67" t="s">
+        <v>8</v>
+      </c>
+      <c r="F67" t="s">
+        <v>13</v>
+      </c>
+      <c r="G67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7">
+      <c r="A68">
+        <v>20330051920322</v>
+      </c>
+      <c r="B68" t="s">
+        <v>32</v>
+      </c>
+      <c r="C68" t="s">
+        <v>54</v>
+      </c>
+      <c r="D68" t="s">
+        <v>154</v>
+      </c>
+      <c r="E68" t="s">
+        <v>8</v>
+      </c>
+      <c r="F68" t="s">
+        <v>14</v>
+      </c>
+      <c r="G68">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7">
+      <c r="A69">
+        <v>20330051920325</v>
+      </c>
+      <c r="B69" t="s">
+        <v>33</v>
+      </c>
+      <c r="C69" t="s">
+        <v>101</v>
+      </c>
+      <c r="D69" t="s">
+        <v>155</v>
+      </c>
+      <c r="E69" t="s">
+        <v>8</v>
+      </c>
+      <c r="F69" t="s">
+        <v>14</v>
+      </c>
+      <c r="G69">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7">
+      <c r="A70">
+        <v>20330051920331</v>
+      </c>
+      <c r="B70" t="s">
+        <v>27</v>
+      </c>
+      <c r="C70" t="s">
+        <v>66</v>
+      </c>
+      <c r="D70" t="s">
+        <v>156</v>
+      </c>
+      <c r="E70" t="s">
+        <v>8</v>
+      </c>
+      <c r="F70" t="s">
+        <v>14</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7">
+      <c r="A71">
         <v>20330051920335</v>
       </c>
-      <c r="B65" t="s">
-        <v>62</v>
-      </c>
-      <c r="C65" t="s">
-        <v>98</v>
-      </c>
-      <c r="D65" t="s">
-        <v>152</v>
-      </c>
-      <c r="E65" t="s">
-        <v>8</v>
-      </c>
-      <c r="F65" t="s">
+      <c r="B71" t="s">
+        <v>64</v>
+      </c>
+      <c r="C71" t="s">
+        <v>102</v>
+      </c>
+      <c r="D71" t="s">
+        <v>157</v>
+      </c>
+      <c r="E71" t="s">
+        <v>8</v>
+      </c>
+      <c r="F71" t="s">
         <v>14</v>
       </c>
-      <c r="G65">
+      <c r="G71">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="168">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>CANUTO</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -169,6 +172,12 @@
     <t>BAEZ</t>
   </si>
   <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ROSETE</t>
+  </si>
+  <si>
     <t>ROJAS</t>
   </si>
   <si>
@@ -181,9 +190,6 @@
     <t>ESPERON</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
     <t>GOMEZ</t>
   </si>
   <si>
@@ -211,9 +217,15 @@
     <t>DE LA ROSA</t>
   </si>
   <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
     <t>VAZQUEZ</t>
   </si>
   <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
     <t>ALAMILLO</t>
   </si>
   <si>
@@ -286,6 +298,9 @@
     <t>LEON</t>
   </si>
   <si>
+    <t>SALAS</t>
+  </si>
+  <si>
     <t>VELASCO</t>
   </si>
   <si>
@@ -322,12 +337,18 @@
     <t>CASTRO</t>
   </si>
   <si>
+    <t>LARA</t>
+  </si>
+  <si>
     <t>CARRILLO</t>
   </si>
   <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
+    <t>ISRAEL</t>
+  </si>
+  <si>
     <t>SAID ANDRES</t>
   </si>
   <si>
@@ -424,12 +445,18 @@
     <t>MARCO ANTONIO</t>
   </si>
   <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>CRISTIAN JAHIR</t>
   </si>
   <si>
+    <t>VICTOR GAEL</t>
+  </si>
+  <si>
     <t>JORGE ALEJANDRO</t>
   </si>
   <si>
@@ -479,6 +506,9 @@
   </si>
   <si>
     <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
   </si>
   <si>
     <t>MARCOS</t>
@@ -1086,16 +1116,19 @@
         <v>26</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="E2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>11.54</v>
+      </c>
+      <c r="H2">
+        <v>7.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1109,16 +1142,19 @@
         <v>26</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E3">
+        <v>0</v>
+      </c>
+      <c r="F3">
         <v>6</v>
       </c>
-      <c r="F3">
-        <v>0</v>
-      </c>
       <c r="G3">
-        <v>0</v>
+        <v>23.08</v>
+      </c>
+      <c r="H3">
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1158,16 +1194,19 @@
         <v>36</v>
       </c>
       <c r="D5">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="E5">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>27.78</v>
+      </c>
+      <c r="H5">
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1181,16 +1220,19 @@
         <v>40</v>
       </c>
       <c r="D6">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="E6">
+        <v>0</v>
+      </c>
+      <c r="F6">
         <v>10</v>
       </c>
-      <c r="F6">
-        <v>0</v>
-      </c>
       <c r="G6">
-        <v>0</v>
+        <v>25</v>
+      </c>
+      <c r="H6">
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1204,16 +1246,19 @@
         <v>18</v>
       </c>
       <c r="D7">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="E7">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>44.44</v>
+      </c>
+      <c r="H7">
+        <v>6.7</v>
       </c>
     </row>
   </sheetData>
@@ -1269,16 +1314,16 @@
         <v>19</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G2">
-        <v>26.92</v>
+        <v>11.54</v>
       </c>
       <c r="H2">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1304,7 +1349,7 @@
         <v>23.08</v>
       </c>
       <c r="H3">
-        <v>8.300000000000001</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1347,16 +1392,16 @@
         <v>25</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F5">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
-        <v>30.56</v>
+        <v>27.78</v>
       </c>
       <c r="H5">
-        <v>7</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1382,7 +1427,7 @@
         <v>25</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1399,16 +1444,16 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G7">
-        <v>50</v>
+        <v>44.44</v>
       </c>
       <c r="H7">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
     </row>
   </sheetData>
@@ -1418,7 +1463,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1450,16 +1495,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920082</v>
+        <v>20330051920073</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="D2" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1473,16 +1518,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920087</v>
+        <v>20330051920082</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>33</v>
+        <v>59</v>
       </c>
       <c r="D3" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1496,16 +1541,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920093</v>
+        <v>20330051920087</v>
       </c>
       <c r="B4" t="s">
         <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>34</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1519,22 +1564,22 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920190</v>
+        <v>20330051920093</v>
       </c>
       <c r="B5" t="s">
         <v>24</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D5" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1542,16 +1587,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920193</v>
+        <v>20330051920190</v>
       </c>
       <c r="B6" t="s">
         <v>25</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>107</v>
+        <v>113</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1565,16 +1610,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920196</v>
+        <v>20330051920193</v>
       </c>
       <c r="B7" t="s">
         <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="D7" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1588,16 +1633,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920213</v>
+        <v>20330051920196</v>
       </c>
       <c r="B8" t="s">
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="D8" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1611,16 +1656,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920214</v>
+        <v>20330051920213</v>
       </c>
       <c r="B9" t="s">
         <v>28</v>
       </c>
       <c r="C9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D9" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1634,16 +1679,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920218</v>
+        <v>20330051920214</v>
       </c>
       <c r="B10" t="s">
         <v>29</v>
       </c>
       <c r="C10" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="D10" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1657,22 +1702,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920278</v>
+        <v>20330051920218</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
       <c r="C11" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1680,22 +1725,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920360</v>
+        <v>20330051920278</v>
       </c>
       <c r="B12" t="s">
         <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="D12" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1703,16 +1748,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920116</v>
+        <v>19330051920360</v>
       </c>
       <c r="B13" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="D13" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1726,16 +1771,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920123</v>
+        <v>20330051920116</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C14" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D14" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1749,19 +1794,19 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920124</v>
+        <v>20330051920123</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
         <v>13</v>
@@ -1775,16 +1820,16 @@
         <v>20330051920124</v>
       </c>
       <c r="B16" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="D16" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="E16" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F16" t="s">
         <v>13</v>
@@ -1795,19 +1840,19 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920125</v>
+        <v>20330051920124</v>
       </c>
       <c r="B17" t="s">
-        <v>21</v>
+        <v>33</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>79</v>
       </c>
       <c r="D17" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F17" t="s">
         <v>13</v>
@@ -1821,16 +1866,16 @@
         <v>20330051920125</v>
       </c>
       <c r="B18" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E18" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F18" t="s">
         <v>13</v>
@@ -1841,19 +1886,19 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920127</v>
+        <v>20330051920125</v>
       </c>
       <c r="B19" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D19" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
       <c r="E19" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
         <v>13</v>
@@ -1867,16 +1912,16 @@
         <v>20330051920127</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F20" t="s">
         <v>13</v>
@@ -1887,19 +1932,19 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920131</v>
+        <v>20330051920127</v>
       </c>
       <c r="B21" t="s">
         <v>34</v>
       </c>
       <c r="C21" t="s">
-        <v>76</v>
+        <v>34</v>
       </c>
       <c r="D21" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
       <c r="E21" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F21" t="s">
         <v>13</v>
@@ -1913,16 +1958,16 @@
         <v>20330051920131</v>
       </c>
       <c r="B22" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C22" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="D22" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="E22" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F22" t="s">
         <v>13</v>
@@ -1933,19 +1978,19 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920134</v>
+        <v>20330051920131</v>
       </c>
       <c r="B23" t="s">
         <v>35</v>
       </c>
       <c r="C23" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="D23" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
         <v>13</v>
@@ -1959,16 +2004,16 @@
         <v>20330051920134</v>
       </c>
       <c r="B24" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C24" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
         <v>13</v>
@@ -1979,19 +2024,19 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920137</v>
+        <v>20330051920134</v>
       </c>
       <c r="B25" t="s">
         <v>36</v>
       </c>
       <c r="C25" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="D25" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="E25" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F25" t="s">
         <v>13</v>
@@ -2005,16 +2050,16 @@
         <v>20330051920137</v>
       </c>
       <c r="B26" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="D26" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F26" t="s">
         <v>13</v>
@@ -2025,19 +2070,19 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>19330051920383</v>
+        <v>20330051920137</v>
       </c>
       <c r="B27" t="s">
         <v>37</v>
       </c>
       <c r="C27" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="D27" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="E27" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
         <v>13</v>
@@ -2051,16 +2096,16 @@
         <v>19330051920383</v>
       </c>
       <c r="B28" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C28" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="E28" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F28" t="s">
         <v>13</v>
@@ -2071,19 +2116,19 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920140</v>
+        <v>19330051920383</v>
       </c>
       <c r="B29" t="s">
         <v>38</v>
       </c>
       <c r="C29" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F29" t="s">
         <v>13</v>
@@ -2097,16 +2142,16 @@
         <v>20330051920140</v>
       </c>
       <c r="B30" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C30" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="D30" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E30" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F30" t="s">
         <v>13</v>
@@ -2117,19 +2162,19 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31">
-        <v>20330051920141</v>
+        <v>20330051920140</v>
       </c>
       <c r="B31" t="s">
         <v>39</v>
       </c>
       <c r="C31" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="D31" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="E31" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F31" t="s">
         <v>13</v>
@@ -2143,16 +2188,16 @@
         <v>20330051920141</v>
       </c>
       <c r="B32" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C32" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="D32" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="E32" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F32" t="s">
         <v>13</v>
@@ -2163,19 +2208,19 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33">
-        <v>20330051920389</v>
+        <v>20330051920141</v>
       </c>
       <c r="B33" t="s">
         <v>40</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E33" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F33" t="s">
         <v>13</v>
@@ -2189,16 +2234,16 @@
         <v>20330051920389</v>
       </c>
       <c r="B34" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C34" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="E34" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F34" t="s">
         <v>13</v>
@@ -2209,19 +2254,19 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35">
-        <v>20330051920387</v>
+        <v>20330051920389</v>
       </c>
       <c r="B35" t="s">
         <v>41</v>
       </c>
       <c r="C35" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="D35" t="s">
-        <v>123</v>
+        <v>132</v>
       </c>
       <c r="E35" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F35" t="s">
         <v>13</v>
@@ -2235,16 +2280,16 @@
         <v>20330051920387</v>
       </c>
       <c r="B36" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C36" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="D36" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="E36" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F36" t="s">
         <v>13</v>
@@ -2255,19 +2300,19 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37">
-        <v>20330051920148</v>
+        <v>20330051920387</v>
       </c>
       <c r="B37" t="s">
-        <v>28</v>
+        <v>42</v>
       </c>
       <c r="C37" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="D37" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="E37" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F37" t="s">
         <v>13</v>
@@ -2281,16 +2326,16 @@
         <v>20330051920148</v>
       </c>
       <c r="B38" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C38" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="D38" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="E38" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F38" t="s">
         <v>13</v>
@@ -2301,16 +2346,19 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39">
-        <v>20330051920153</v>
+        <v>20330051920148</v>
       </c>
       <c r="B39" t="s">
-        <v>42</v>
+        <v>29</v>
+      </c>
+      <c r="C39" t="s">
+        <v>88</v>
       </c>
       <c r="D39" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E39" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F39" t="s">
         <v>13</v>
@@ -2324,13 +2372,13 @@
         <v>20330051920153</v>
       </c>
       <c r="B40" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D40" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="E40" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F40" t="s">
         <v>13</v>
@@ -2341,16 +2389,13 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41">
-        <v>19330051920399</v>
+        <v>20330051920153</v>
       </c>
       <c r="B41" t="s">
         <v>43</v>
       </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
       <c r="D41" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="E41" t="s">
         <v>9</v>
@@ -2364,22 +2409,22 @@
     </row>
     <row r="42" spans="1:7">
       <c r="A42">
-        <v>20330051920317</v>
+        <v>19330051920399</v>
       </c>
       <c r="B42" t="s">
         <v>44</v>
       </c>
       <c r="C42" t="s">
-        <v>26</v>
+        <v>89</v>
       </c>
       <c r="D42" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="E42" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F42" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G42">
         <v>2</v>
@@ -2387,16 +2432,16 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43">
-        <v>20330051920397</v>
+        <v>20330051920317</v>
       </c>
       <c r="B43" t="s">
         <v>45</v>
       </c>
       <c r="C43" t="s">
-        <v>86</v>
+        <v>27</v>
       </c>
       <c r="D43" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="E43" t="s">
         <v>8</v>
@@ -2410,16 +2455,16 @@
     </row>
     <row r="44" spans="1:7">
       <c r="A44">
-        <v>20330051920326</v>
+        <v>20330051920397</v>
       </c>
       <c r="B44" t="s">
         <v>46</v>
       </c>
       <c r="C44" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
       <c r="D44" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="E44" t="s">
         <v>8</v>
@@ -2433,16 +2478,16 @@
     </row>
     <row r="45" spans="1:7">
       <c r="A45">
-        <v>20330051920329</v>
+        <v>20330051920326</v>
       </c>
       <c r="B45" t="s">
         <v>47</v>
       </c>
       <c r="C45" t="s">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c r="D45" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E45" t="s">
         <v>8</v>
@@ -2456,16 +2501,16 @@
     </row>
     <row r="46" spans="1:7">
       <c r="A46">
-        <v>20330051920330</v>
+        <v>20330051920329</v>
       </c>
       <c r="B46" t="s">
         <v>48</v>
       </c>
       <c r="C46" t="s">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="D46" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="E46" t="s">
         <v>8</v>
@@ -2479,39 +2524,39 @@
     </row>
     <row r="47" spans="1:7">
       <c r="A47">
-        <v>20330051920071</v>
+        <v>20330051920330</v>
       </c>
       <c r="B47" t="s">
         <v>49</v>
       </c>
       <c r="C47" t="s">
-        <v>54</v>
+        <v>74</v>
       </c>
       <c r="D47" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="E47" t="s">
         <v>8</v>
       </c>
       <c r="F47" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G47">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="48" spans="1:7">
       <c r="A48">
-        <v>20330051920080</v>
+        <v>20330051920071</v>
       </c>
       <c r="B48" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="C48" t="s">
-        <v>88</v>
+        <v>51</v>
       </c>
       <c r="D48" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="E48" t="s">
         <v>8</v>
@@ -2525,16 +2570,16 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49">
-        <v>20330051920081</v>
+        <v>18330051920156</v>
       </c>
       <c r="B49" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="C49" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="D49" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E49" t="s">
         <v>8</v>
@@ -2548,16 +2593,16 @@
     </row>
     <row r="50" spans="1:7">
       <c r="A50">
-        <v>20330051920064</v>
+        <v>20330051920080</v>
       </c>
       <c r="B50" t="s">
-        <v>50</v>
+        <v>22</v>
       </c>
       <c r="C50" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D50" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E50" t="s">
         <v>8</v>
@@ -2571,16 +2616,16 @@
     </row>
     <row r="51" spans="1:7">
       <c r="A51">
-        <v>20330051920068</v>
+        <v>20330051920081</v>
       </c>
       <c r="B51" t="s">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C51" t="s">
-        <v>21</v>
+        <v>38</v>
       </c>
       <c r="D51" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E51" t="s">
         <v>8</v>
@@ -2594,22 +2639,22 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52">
-        <v>20330051920191</v>
+        <v>20330051920063</v>
       </c>
       <c r="B52" t="s">
         <v>52</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D52" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E52" t="s">
         <v>8</v>
       </c>
       <c r="F52" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G52">
         <v>1</v>
@@ -2617,22 +2662,22 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53">
-        <v>20330051920197</v>
+        <v>20330051920064</v>
       </c>
       <c r="B53" t="s">
         <v>53</v>
       </c>
       <c r="C53" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="D53" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
         <v>8</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G53">
         <v>1</v>
@@ -2640,22 +2685,22 @@
     </row>
     <row r="54" spans="1:7">
       <c r="A54">
-        <v>20330051920198</v>
+        <v>20330051920068</v>
       </c>
       <c r="B54" t="s">
         <v>54</v>
       </c>
       <c r="C54" t="s">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="D54" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E54" t="s">
         <v>8</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G54">
         <v>1</v>
@@ -2663,16 +2708,16 @@
     </row>
     <row r="55" spans="1:7">
       <c r="A55">
-        <v>20330051920199</v>
+        <v>20330051920191</v>
       </c>
       <c r="B55" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="D55" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E55" t="s">
         <v>8</v>
@@ -2686,16 +2731,16 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56">
-        <v>20330051920201</v>
+        <v>20330051920197</v>
       </c>
       <c r="B56" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C56" t="s">
-        <v>21</v>
+        <v>96</v>
       </c>
       <c r="D56" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E56" t="s">
         <v>8</v>
@@ -2709,16 +2754,16 @@
     </row>
     <row r="57" spans="1:7">
       <c r="A57">
-        <v>20330051920202</v>
+        <v>20330051920198</v>
       </c>
       <c r="B57" t="s">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="C57" t="s">
-        <v>66</v>
+        <v>97</v>
       </c>
       <c r="D57" t="s">
-        <v>116</v>
+        <v>150</v>
       </c>
       <c r="E57" t="s">
         <v>8</v>
@@ -2732,16 +2777,16 @@
     </row>
     <row r="58" spans="1:7">
       <c r="A58">
-        <v>19330051920290</v>
+        <v>20330051920199</v>
       </c>
       <c r="B58" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C58" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="D58" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="E58" t="s">
         <v>8</v>
@@ -2755,16 +2800,16 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59">
-        <v>20330051920210</v>
+        <v>20330051920201</v>
       </c>
       <c r="B59" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C59" t="s">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="D59" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="E59" t="s">
         <v>8</v>
@@ -2778,16 +2823,16 @@
     </row>
     <row r="60" spans="1:7">
       <c r="A60">
-        <v>20330051920215</v>
+        <v>20330051920202</v>
       </c>
       <c r="B60" t="s">
-        <v>28</v>
+        <v>58</v>
       </c>
       <c r="C60" t="s">
-        <v>33</v>
+        <v>70</v>
       </c>
       <c r="D60" t="s">
-        <v>146</v>
+        <v>123</v>
       </c>
       <c r="E60" t="s">
         <v>8</v>
@@ -2801,16 +2846,16 @@
     </row>
     <row r="61" spans="1:7">
       <c r="A61">
-        <v>20330051920217</v>
+        <v>19330051920290</v>
       </c>
       <c r="B61" t="s">
-        <v>28</v>
+        <v>59</v>
       </c>
       <c r="C61" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="D61" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E61" t="s">
         <v>8</v>
@@ -2824,22 +2869,22 @@
     </row>
     <row r="62" spans="1:7">
       <c r="A62">
-        <v>18330051920393</v>
+        <v>20330051920210</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C62" t="s">
-        <v>96</v>
+        <v>70</v>
       </c>
       <c r="D62" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E62" t="s">
         <v>8</v>
       </c>
       <c r="F62" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2847,22 +2892,22 @@
     </row>
     <row r="63" spans="1:7">
       <c r="A63">
-        <v>20330051920121</v>
+        <v>20330051920215</v>
       </c>
       <c r="B63" t="s">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C63" t="s">
-        <v>97</v>
+        <v>34</v>
       </c>
       <c r="D63" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E63" t="s">
         <v>8</v>
       </c>
       <c r="F63" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2870,22 +2915,22 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64">
-        <v>20330051920128</v>
+        <v>20330051920217</v>
       </c>
       <c r="B64" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C64" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="D64" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="E64" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F64" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -2893,19 +2938,19 @@
     </row>
     <row r="65" spans="1:7">
       <c r="A65">
-        <v>20330051920139</v>
+        <v>18330051920393</v>
       </c>
       <c r="B65" t="s">
         <v>61</v>
       </c>
       <c r="C65" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="D65" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E65" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F65" t="s">
         <v>13</v>
@@ -2916,19 +2961,19 @@
     </row>
     <row r="66" spans="1:7">
       <c r="A66">
-        <v>19330051920387</v>
+        <v>20330051920121</v>
       </c>
       <c r="B66" t="s">
         <v>62</v>
       </c>
       <c r="C66" t="s">
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="D66" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E66" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F66" t="s">
         <v>13</v>
@@ -2939,19 +2984,19 @@
     </row>
     <row r="67" spans="1:7">
       <c r="A67">
-        <v>20330051920144</v>
+        <v>20330051920128</v>
       </c>
       <c r="B67" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="C67" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="D67" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E67" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F67" t="s">
         <v>13</v>
@@ -2962,22 +3007,22 @@
     </row>
     <row r="68" spans="1:7">
       <c r="A68">
-        <v>20330051920322</v>
+        <v>20330051920139</v>
       </c>
       <c r="B68" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="C68" t="s">
-        <v>54</v>
+        <v>104</v>
       </c>
       <c r="D68" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E68" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G68">
         <v>1</v>
@@ -2985,22 +3030,22 @@
     </row>
     <row r="69" spans="1:7">
       <c r="A69">
-        <v>20330051920325</v>
+        <v>19330051920387</v>
       </c>
       <c r="B69" t="s">
+        <v>64</v>
+      </c>
+      <c r="C69" t="s">
         <v>33</v>
       </c>
-      <c r="C69" t="s">
-        <v>101</v>
-      </c>
       <c r="D69" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E69" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F69" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G69">
         <v>1</v>
@@ -3008,22 +3053,22 @@
     </row>
     <row r="70" spans="1:7">
       <c r="A70">
-        <v>20330051920331</v>
+        <v>20330051920144</v>
       </c>
       <c r="B70" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="C70" t="s">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="D70" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E70" t="s">
         <v>8</v>
       </c>
       <c r="F70" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G70">
         <v>1</v>
@@ -3031,16 +3076,16 @@
     </row>
     <row r="71" spans="1:7">
       <c r="A71">
-        <v>20330051920335</v>
+        <v>20330051920320</v>
       </c>
       <c r="B71" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C71" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="D71" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E71" t="s">
         <v>8</v>
@@ -3049,6 +3094,98 @@
         <v>14</v>
       </c>
       <c r="G71">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7">
+      <c r="A72">
+        <v>20330051920322</v>
+      </c>
+      <c r="B72" t="s">
+        <v>33</v>
+      </c>
+      <c r="C72" t="s">
+        <v>51</v>
+      </c>
+      <c r="D72" t="s">
+        <v>164</v>
+      </c>
+      <c r="E72" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7">
+      <c r="A73">
+        <v>20330051920325</v>
+      </c>
+      <c r="B73" t="s">
+        <v>34</v>
+      </c>
+      <c r="C73" t="s">
+        <v>107</v>
+      </c>
+      <c r="D73" t="s">
+        <v>165</v>
+      </c>
+      <c r="E73" t="s">
+        <v>8</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7">
+      <c r="A74">
+        <v>20330051920331</v>
+      </c>
+      <c r="B74" t="s">
+        <v>28</v>
+      </c>
+      <c r="C74" t="s">
+        <v>70</v>
+      </c>
+      <c r="D74" t="s">
+        <v>166</v>
+      </c>
+      <c r="E74" t="s">
+        <v>8</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7">
+      <c r="A75">
+        <v>20330051920335</v>
+      </c>
+      <c r="B75" t="s">
+        <v>67</v>
+      </c>
+      <c r="C75" t="s">
+        <v>108</v>
+      </c>
+      <c r="D75" t="s">
+        <v>167</v>
+      </c>
+      <c r="E75" t="s">
+        <v>8</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="69">
   <si>
     <t>Mat</t>
   </si>
@@ -55,9 +55,6 @@
     <t>5ALCV</t>
   </si>
   <si>
-    <t>5APV</t>
-  </si>
-  <si>
     <t>5ARHV</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
     <t>BRETON</t>
   </si>
   <si>
@@ -145,9 +139,6 @@
     <t>HUERTA</t>
   </si>
   <si>
-    <t>XOTLANIHUA</t>
-  </si>
-  <si>
     <t>VICENTE</t>
   </si>
   <si>
@@ -194,9 +185,6 @@
   </si>
   <si>
     <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>MARCO JOSAFAT</t>
   </si>
   <si>
     <t>AMYRA NAHOMY</t>
@@ -593,7 +581,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -685,99 +673,73 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="G4">
-        <v>68.42</v>
+        <v>80.56</v>
       </c>
       <c r="H4">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>80.56</v>
+        <v>77.5</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>14</v>
       </c>
       <c r="G6">
-        <v>77.5</v>
+        <v>77.78</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="F7">
-        <v>14</v>
-      </c>
-      <c r="G7">
-        <v>77.78</v>
-      </c>
-      <c r="H7">
         <v>6</v>
       </c>
     </row>
@@ -788,7 +750,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -880,99 +842,73 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>78.95</v>
+        <v>77.78</v>
       </c>
       <c r="H4">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>77.78</v>
+        <v>77.5</v>
       </c>
       <c r="H5">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>77.5</v>
+        <v>72.22</v>
       </c>
       <c r="H6">
-        <v>8.199999999999999</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>72.22</v>
-      </c>
-      <c r="H7">
         <v>6</v>
       </c>
     </row>
@@ -983,7 +919,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
@@ -1075,99 +1011,73 @@
         <v>12</v>
       </c>
       <c r="C4">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F4">
-        <v>15</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>78.95</v>
+        <v>77.78</v>
       </c>
       <c r="H4">
-        <v>7.3</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F5">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>77.78</v>
+        <v>77.5</v>
       </c>
       <c r="H5">
-        <v>7.7</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>13</v>
       </c>
       <c r="C6">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>0</v>
       </c>
       <c r="E6">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F6">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="G6">
-        <v>77.5</v>
+        <v>72.22</v>
       </c>
       <c r="H6">
-        <v>8.4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C7">
-        <v>18</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>5</v>
-      </c>
-      <c r="F7">
-        <v>13</v>
-      </c>
-      <c r="G7">
-        <v>72.22</v>
-      </c>
-      <c r="H7">
         <v>6.2</v>
       </c>
     </row>
@@ -1178,7 +1088,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G20"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1187,25 +1097,25 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>19</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1213,13 +1123,13 @@
         <v>20330051920073</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="D2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1236,13 +1146,13 @@
         <v>20330051920082</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1259,13 +1169,13 @@
         <v>20330051920190</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="D4" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1282,13 +1192,13 @@
         <v>20330051920196</v>
       </c>
       <c r="B5" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D5" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1305,13 +1215,13 @@
         <v>20330051920214</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="D6" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1325,19 +1235,19 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920278</v>
+        <v>19330051920360</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="D7" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F7" t="s">
         <v>12</v>
@@ -1348,19 +1258,19 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920360</v>
+        <v>20330051920317</v>
       </c>
       <c r="B8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>43</v>
+        <v>23</v>
       </c>
       <c r="D8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
         <v>13</v>
@@ -1371,22 +1281,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920317</v>
+        <v>20330051920397</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>41</v>
       </c>
       <c r="D9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1394,22 +1304,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920397</v>
+        <v>20330051920326</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1417,22 +1327,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920326</v>
+        <v>20330051920329</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="D11" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1440,39 +1350,39 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920329</v>
+        <v>20330051920071</v>
       </c>
       <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="s">
         <v>31</v>
       </c>
-      <c r="C12" t="s">
-        <v>46</v>
-      </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G12">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920071</v>
+        <v>18330051920156</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>44</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1486,16 +1396,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>18330051920156</v>
+        <v>20330051920080</v>
       </c>
       <c r="B14" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D14" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1509,16 +1419,16 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920080</v>
+        <v>20330051920063</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D15" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1532,22 +1442,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920063</v>
+        <v>20330051920191</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1555,16 +1465,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920191</v>
+        <v>20330051920198</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C17" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D17" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1578,16 +1488,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920198</v>
+        <v>20330051920217</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
       <c r="C18" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D18" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1601,47 +1511,24 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920217</v>
+        <v>20330051920320</v>
       </c>
       <c r="B19" t="s">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c r="C19" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="G19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>20330051920320</v>
-      </c>
-      <c r="B20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" t="s">
-        <v>72</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>14</v>
-      </c>
-      <c r="G20">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
   <si>
     <t>Mat</t>
   </si>
@@ -82,6 +82,9 @@
     <t>CANUTO</t>
   </si>
   <si>
+    <t>DE LA CRUZ</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
@@ -97,6 +100,12 @@
     <t>BRETON</t>
   </si>
   <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
     <t>APALE</t>
   </si>
   <si>
@@ -127,6 +136,9 @@
     <t>MEDINA</t>
   </si>
   <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
@@ -142,6 +154,9 @@
     <t>VICENTE</t>
   </si>
   <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>RODRIGUEZ</t>
   </si>
   <si>
@@ -151,9 +166,6 @@
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
     <t>LEON</t>
   </si>
   <si>
@@ -175,6 +187,9 @@
     <t>ISRAEL</t>
   </si>
   <si>
+    <t>JESUS ISRAEL</t>
+  </si>
+  <si>
     <t>SAID ANDRES</t>
   </si>
   <si>
@@ -188,6 +203,12 @@
   </si>
   <si>
     <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
   </si>
   <si>
     <t>JOSE MIGUEL</t>
@@ -699,10 +720,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>9</v>
@@ -711,7 +732,7 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
@@ -868,10 +889,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>9</v>
@@ -880,7 +901,7 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="H5">
         <v>8.199999999999999</v>
@@ -1037,10 +1058,10 @@
         <v>12</v>
       </c>
       <c r="C5">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>9</v>
@@ -1049,7 +1070,7 @@
         <v>31</v>
       </c>
       <c r="G5">
-        <v>77.5</v>
+        <v>73.81</v>
       </c>
       <c r="H5">
         <v>8.4</v>
@@ -1088,7 +1109,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1126,10 +1147,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1143,16 +1164,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920082</v>
+        <v>19330051920051</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="D3" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1166,22 +1187,22 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920190</v>
+        <v>20330051920082</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="D4" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2</v>
@@ -1189,16 +1210,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920196</v>
+        <v>20330051920190</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D5" t="s">
-        <v>54</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1212,16 +1233,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920214</v>
+        <v>20330051920196</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="D6" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1235,22 +1256,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>19330051920360</v>
+        <v>20330051920214</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="D7" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1258,22 +1279,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920317</v>
+        <v>19330051920360</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>44</v>
       </c>
       <c r="D8" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="E8" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1281,22 +1302,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920397</v>
+        <v>19330051920436</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D9" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1304,22 +1325,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920326</v>
+        <v>19330051920393</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E10" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F10" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1327,16 +1348,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920329</v>
+        <v>20330051920317</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1350,85 +1371,85 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920071</v>
+        <v>20330051920397</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="D12" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="E12" t="s">
         <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G12">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>18330051920156</v>
+        <v>20330051920326</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D13" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
       </c>
       <c r="F13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G13">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920080</v>
+        <v>20330051920329</v>
       </c>
       <c r="B14" t="s">
-        <v>21</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="D14" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920063</v>
+        <v>20330051920071</v>
       </c>
       <c r="B15" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
@@ -1442,22 +1463,22 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920191</v>
+        <v>18330051920156</v>
       </c>
       <c r="B16" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1465,22 +1486,22 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920198</v>
+        <v>20330051920080</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G17">
         <v>1</v>
@@ -1488,22 +1509,22 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920217</v>
+        <v>20330051920063</v>
       </c>
       <c r="B18" t="s">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D18" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G18">
         <v>1</v>
@@ -1511,24 +1532,93 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
+        <v>20330051920191</v>
+      </c>
+      <c r="B19" t="s">
+        <v>36</v>
+      </c>
+      <c r="C19" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7">
+      <c r="A20">
+        <v>20330051920198</v>
+      </c>
+      <c r="B20" t="s">
+        <v>34</v>
+      </c>
+      <c r="C20" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" t="s">
+        <v>73</v>
+      </c>
+      <c r="E20" t="s">
+        <v>8</v>
+      </c>
+      <c r="F20" t="s">
+        <v>11</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7">
+      <c r="A21">
+        <v>20330051920217</v>
+      </c>
+      <c r="B21" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" t="s">
+        <v>74</v>
+      </c>
+      <c r="E21" t="s">
+        <v>8</v>
+      </c>
+      <c r="F21" t="s">
+        <v>11</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7">
+      <c r="A22">
         <v>20330051920320</v>
       </c>
-      <c r="B19" t="s">
-        <v>34</v>
-      </c>
-      <c r="C19" t="s">
-        <v>50</v>
-      </c>
-      <c r="D19" t="s">
-        <v>68</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
+      <c r="B22" t="s">
+        <v>37</v>
+      </c>
+      <c r="C22" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
         <v>13</v>
       </c>
-      <c r="G19">
+      <c r="G22">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="89">
   <si>
     <t>Mat</t>
   </si>
@@ -91,12 +91,18 @@
     <t>ASCENCION</t>
   </si>
   <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
     <t>BRETON</t>
   </si>
   <si>
@@ -124,15 +130,24 @@
     <t>FLORES</t>
   </si>
   <si>
-    <t>ROSETE</t>
-  </si>
-  <si>
     <t>ARIAS</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
     <t>CANTELLAN</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
     <t>MEDINA</t>
   </si>
   <si>
@@ -145,12 +160,18 @@
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>GOMEZ</t>
+  </si>
+  <si>
     <t>MORENO</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
     <t>VICENTE</t>
   </si>
   <si>
@@ -169,9 +190,6 @@
     <t>LEON</t>
   </si>
   <si>
-    <t>SALAS</t>
-  </si>
-  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -181,9 +199,15 @@
     <t>SOLIS</t>
   </si>
   <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
     <t>LARA</t>
   </si>
   <si>
+    <t>TZIZIHUA</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
   </si>
   <si>
@@ -196,12 +220,18 @@
     <t>REYNA ARISBETH</t>
   </si>
   <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
     <t>ERICK DE JESUS</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
   </si>
   <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
     <t>AMYRA NAHOMY</t>
   </si>
   <si>
@@ -232,9 +262,6 @@
     <t>LUIS ENRIQUE</t>
   </si>
   <si>
-    <t>VICTOR GAEL</t>
-  </si>
-  <si>
     <t>ANALI</t>
   </si>
   <si>
@@ -244,7 +271,19 @@
     <t>LUIS DIEGO</t>
   </si>
   <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
     <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
+  </si>
+  <si>
+    <t>MICHELLE ROBERTA</t>
+  </si>
+  <si>
+    <t>DORA LUZ</t>
   </si>
 </sst>
 </file>
@@ -986,16 +1025,16 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G2">
-        <v>30.77</v>
+        <v>34.62</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1012,16 +1051,16 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F3">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3">
-        <v>61.54</v>
+        <v>53.85</v>
       </c>
       <c r="H3">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -1047,7 +1086,7 @@
         <v>77.78</v>
       </c>
       <c r="H4">
-        <v>7.7</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -1064,16 +1103,16 @@
         <v>2</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>73.81</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="H5">
-        <v>8.4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1090,16 +1129,16 @@
         <v>0</v>
       </c>
       <c r="E6">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F6">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G6">
-        <v>72.22</v>
+        <v>55.56</v>
       </c>
       <c r="H6">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
     </row>
   </sheetData>
@@ -1109,7 +1148,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1147,10 +1186,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1170,10 +1209,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1193,10 +1232,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1216,10 +1255,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1233,16 +1272,16 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920196</v>
+        <v>20330051920193</v>
       </c>
       <c r="B6" t="s">
         <v>24</v>
       </c>
       <c r="C6" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1256,16 +1295,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920214</v>
+        <v>20330051920196</v>
       </c>
       <c r="B7" t="s">
         <v>25</v>
       </c>
       <c r="C7" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1279,22 +1318,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>19330051920360</v>
+        <v>20330051920214</v>
       </c>
       <c r="B8" t="s">
         <v>26</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="E8" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1302,22 +1341,22 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920436</v>
+        <v>20330051920218</v>
       </c>
       <c r="B9" t="s">
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="E9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9">
         <v>2</v>
@@ -1325,16 +1364,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920393</v>
+        <v>19330051920360</v>
       </c>
       <c r="B10" t="s">
         <v>28</v>
       </c>
       <c r="C10" t="s">
-        <v>21</v>
+        <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="E10" t="s">
         <v>9</v>
@@ -1348,22 +1387,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920317</v>
+        <v>19330051920436</v>
       </c>
       <c r="B11" t="s">
         <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>24</v>
+        <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="E11" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1371,22 +1410,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920397</v>
+        <v>19330051920393</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>46</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1394,16 +1433,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920326</v>
+        <v>20330051920317</v>
       </c>
       <c r="B13" t="s">
         <v>31</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="E13" t="s">
         <v>8</v>
@@ -1417,16 +1456,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920329</v>
+        <v>20330051920397</v>
       </c>
       <c r="B14" t="s">
         <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="D14" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="E14" t="s">
         <v>8</v>
@@ -1440,62 +1479,62 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920071</v>
+        <v>20330051920326</v>
       </c>
       <c r="B15" t="s">
         <v>33</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G15">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>18330051920156</v>
+        <v>20330051920329</v>
       </c>
       <c r="B16" t="s">
         <v>34</v>
       </c>
       <c r="C16" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="D16" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G16">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920080</v>
+        <v>20330051920071</v>
       </c>
       <c r="B17" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C17" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="D17" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1509,16 +1548,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920063</v>
+        <v>18330051920156</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D18" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1532,22 +1571,22 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920191</v>
+        <v>20330051920080</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D19" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G19">
         <v>1</v>
@@ -1555,16 +1594,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920198</v>
+        <v>20330051920191</v>
       </c>
       <c r="B20" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D20" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1578,16 +1617,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920217</v>
+        <v>20330051920198</v>
       </c>
       <c r="B21" t="s">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="C21" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="D21" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1601,24 +1640,139 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
+        <v>20330051920217</v>
+      </c>
+      <c r="B22" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" t="s">
+        <v>59</v>
+      </c>
+      <c r="D22" t="s">
+        <v>83</v>
+      </c>
+      <c r="E22" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" t="s">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23">
+        <v>19330051920383</v>
+      </c>
+      <c r="B23" t="s">
+        <v>38</v>
+      </c>
+      <c r="C23" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" t="s">
+        <v>84</v>
+      </c>
+      <c r="E23" t="s">
+        <v>9</v>
+      </c>
+      <c r="F23" t="s">
+        <v>12</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24">
         <v>20330051920320</v>
       </c>
-      <c r="B22" t="s">
-        <v>37</v>
-      </c>
-      <c r="C22" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" t="s">
-        <v>75</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
+      <c r="B24" t="s">
+        <v>39</v>
+      </c>
+      <c r="C24" t="s">
+        <v>61</v>
+      </c>
+      <c r="D24" t="s">
+        <v>85</v>
+      </c>
+      <c r="E24" t="s">
+        <v>8</v>
+      </c>
+      <c r="F24" t="s">
         <v>13</v>
       </c>
-      <c r="G22">
+      <c r="G24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7">
+      <c r="A25">
+        <v>20330051920322</v>
+      </c>
+      <c r="B25" t="s">
+        <v>40</v>
+      </c>
+      <c r="C25" t="s">
+        <v>36</v>
+      </c>
+      <c r="D25" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" t="s">
+        <v>8</v>
+      </c>
+      <c r="F25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7">
+      <c r="A26">
+        <v>20330051920331</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+      <c r="C26" t="s">
+        <v>46</v>
+      </c>
+      <c r="D26" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" t="s">
+        <v>8</v>
+      </c>
+      <c r="F26" t="s">
+        <v>13</v>
+      </c>
+      <c r="G26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7">
+      <c r="A27">
+        <v>20330051920335</v>
+      </c>
+      <c r="B27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" t="s">
+        <v>8</v>
+      </c>
+      <c r="F27" t="s">
+        <v>13</v>
+      </c>
+      <c r="G27">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
   <si>
     <t>Mat</t>
   </si>
@@ -79,6 +79,9 @@
     <t>Reprobadas</t>
   </si>
   <si>
+    <t>BAEZ</t>
+  </si>
+  <si>
     <t>CANUTO</t>
   </si>
   <si>
@@ -88,6 +91,9 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>TEXCAHUA</t>
+  </si>
+  <si>
     <t>ASCENCION</t>
   </si>
   <si>
@@ -124,9 +130,6 @@
     <t>NAJERA</t>
   </si>
   <si>
-    <t>BAEZ</t>
-  </si>
-  <si>
     <t>FLORES</t>
   </si>
   <si>
@@ -154,9 +157,15 @@
     <t>CRUZ</t>
   </si>
   <si>
+    <t>LEON</t>
+  </si>
+  <si>
     <t>OFICIAL</t>
   </si>
   <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -187,9 +196,6 @@
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>LEON</t>
-  </si>
-  <si>
     <t>BARRAGAN</t>
   </si>
   <si>
@@ -208,15 +214,24 @@
     <t>TZIZIHUA</t>
   </si>
   <si>
+    <t>MARCO ANTONIO</t>
+  </si>
+  <si>
     <t>ISRAEL</t>
   </si>
   <si>
     <t>JESUS ISRAEL</t>
   </si>
   <si>
+    <t>LUIS ENRIQUE</t>
+  </si>
+  <si>
     <t>SAID ANDRES</t>
   </si>
   <si>
+    <t>OSVALDO</t>
+  </si>
+  <si>
     <t>REYNA ARISBETH</t>
   </si>
   <si>
@@ -253,13 +268,7 @@
     <t>JUAN GUILLERMO</t>
   </si>
   <si>
-    <t>MARCO ANTONIO</t>
-  </si>
-  <si>
     <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>LUIS ENRIQUE</t>
   </si>
   <si>
     <t>ANALI</t>
@@ -1148,7 +1157,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G27"/>
+  <dimension ref="A1:G28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1180,16 +1189,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920073</v>
+        <v>20330051920071</v>
       </c>
       <c r="B2" t="s">
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="D2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1203,7 +1212,7 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920051</v>
+        <v>20330051920073</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
@@ -1212,7 +1221,7 @@
         <v>44</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1226,7 +1235,7 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920082</v>
+        <v>19330051920051</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
@@ -1235,7 +1244,7 @@
         <v>45</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1249,7 +1258,7 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920190</v>
+        <v>20330051920080</v>
       </c>
       <c r="B5" t="s">
         <v>23</v>
@@ -1258,13 +1267,13 @@
         <v>46</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2</v>
@@ -1272,22 +1281,22 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920193</v>
+        <v>20330051920082</v>
       </c>
       <c r="B6" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C6" t="s">
         <v>47</v>
       </c>
       <c r="D6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>2</v>
@@ -1295,22 +1304,22 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920196</v>
+        <v>20330051920070</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C7" t="s">
         <v>48</v>
       </c>
       <c r="D7" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>2</v>
@@ -1318,16 +1327,16 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920214</v>
+        <v>20330051920190</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>49</v>
       </c>
       <c r="D8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1341,16 +1350,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920218</v>
+        <v>20330051920193</v>
       </c>
       <c r="B9" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C9" t="s">
         <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1364,22 +1373,22 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>19330051920360</v>
+        <v>20330051920196</v>
       </c>
       <c r="B10" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E10" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G10">
         <v>2</v>
@@ -1387,22 +1396,22 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>19330051920436</v>
+        <v>20330051920214</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
         <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G11">
         <v>2</v>
@@ -1410,22 +1419,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920393</v>
+        <v>20330051920218</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>53</v>
       </c>
       <c r="D12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1433,22 +1442,22 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>20330051920317</v>
+        <v>19330051920360</v>
       </c>
       <c r="B13" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>25</v>
+        <v>54</v>
       </c>
       <c r="D13" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E13" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F13" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G13">
         <v>2</v>
@@ -1456,22 +1465,22 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>20330051920397</v>
+        <v>19330051920436</v>
       </c>
       <c r="B14" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D14" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E14" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G14">
         <v>2</v>
@@ -1479,22 +1488,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920326</v>
+        <v>19330051920393</v>
       </c>
       <c r="B15" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>22</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E15" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1502,16 +1511,16 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920329</v>
+        <v>20330051920317</v>
       </c>
       <c r="B16" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="D16" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
@@ -1525,91 +1534,91 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920071</v>
+        <v>20330051920397</v>
       </c>
       <c r="B17" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>56</v>
       </c>
       <c r="D17" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G17">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>18330051920156</v>
+        <v>20330051920326</v>
       </c>
       <c r="B18" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D18" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G18">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920080</v>
+        <v>20330051920329</v>
       </c>
       <c r="B19" t="s">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D19" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="G19">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920191</v>
+        <v>18330051920156</v>
       </c>
       <c r="B20" t="s">
         <v>37</v>
       </c>
       <c r="C20" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="D20" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1617,16 +1626,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920198</v>
+        <v>20330051920191</v>
       </c>
       <c r="B21" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C21" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1640,16 +1649,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920217</v>
+        <v>20330051920198</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C22" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1663,22 +1672,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>19330051920383</v>
+        <v>20330051920217</v>
       </c>
       <c r="B23" t="s">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E23" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F23" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1686,22 +1695,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920320</v>
+        <v>19330051920383</v>
       </c>
       <c r="B24" t="s">
         <v>39</v>
       </c>
       <c r="C24" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1709,16 +1718,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920322</v>
+        <v>20330051920320</v>
       </c>
       <c r="B25" t="s">
         <v>40</v>
       </c>
       <c r="C25" t="s">
-        <v>36</v>
+        <v>63</v>
       </c>
       <c r="D25" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1732,16 +1741,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920331</v>
+        <v>20330051920322</v>
       </c>
       <c r="B26" t="s">
         <v>41</v>
       </c>
       <c r="C26" t="s">
-        <v>46</v>
+        <v>37</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1755,16 +1764,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920335</v>
+        <v>20330051920331</v>
       </c>
       <c r="B27" t="s">
         <v>42</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="D27" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1773,6 +1782,29 @@
         <v>13</v>
       </c>
       <c r="G27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7">
+      <c r="A28">
+        <v>20330051920335</v>
+      </c>
+      <c r="B28" t="s">
+        <v>43</v>
+      </c>
+      <c r="C28" t="s">
+        <v>64</v>
+      </c>
+      <c r="D28" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" t="s">
+        <v>8</v>
+      </c>
+      <c r="F28" t="s">
+        <v>13</v>
+      </c>
+      <c r="G28">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="96">
   <si>
     <t>Mat</t>
   </si>
@@ -91,100 +91,121 @@
     <t>GONZALEZ</t>
   </si>
   <si>
+    <t>OLMOS</t>
+  </si>
+  <si>
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>XOTLANIHUA</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>RAMOS</t>
+  </si>
+  <si>
+    <t>ROJAS</t>
+  </si>
+  <si>
+    <t>APALE</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
     <t>ASCENCION</t>
   </si>
   <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
     <t>CARRERA</t>
   </si>
   <si>
+    <t>MENDEZ</t>
+  </si>
+  <si>
+    <t>CANTELLAN</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>IBAÑEZ</t>
+  </si>
+  <si>
+    <t>LUNA</t>
+  </si>
+  <si>
+    <t>NAJERA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>VAZQUEZ</t>
+  </si>
+  <si>
+    <t>MEDINA</t>
+  </si>
+  <si>
+    <t>CRUZ</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>OFICIAL</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>RAMIREZ</t>
+  </si>
+  <si>
+    <t>VICENTE</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
     <t>ESTEVEZ</t>
   </si>
   <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
-    <t>BRETON</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>IBAÑEZ</t>
-  </si>
-  <si>
-    <t>LUNA</t>
-  </si>
-  <si>
-    <t>NAJERA</t>
-  </si>
-  <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
-    <t>CANTELLAN</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>VAZQUEZ</t>
-  </si>
-  <si>
-    <t>MEDINA</t>
-  </si>
-  <si>
-    <t>CRUZ</t>
-  </si>
-  <si>
-    <t>LEON</t>
-  </si>
-  <si>
-    <t>OFICIAL</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>GOMEZ</t>
   </si>
   <si>
-    <t>MORENO</t>
+    <t>ROQUE</t>
   </si>
   <si>
     <t>HUERTA</t>
   </si>
   <si>
-    <t>RAMIREZ</t>
-  </si>
-  <si>
-    <t>VICENTE</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
+    <t>SOLIS</t>
+  </si>
+  <si>
+    <t>SANTOS</t>
+  </si>
+  <si>
+    <t>LARA</t>
   </si>
   <si>
     <t>RODRIGUEZ</t>
@@ -196,21 +217,6 @@
     <t>MONTALVO</t>
   </si>
   <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ROQUE</t>
-  </si>
-  <si>
-    <t>SOLIS</t>
-  </si>
-  <si>
-    <t>SANTOS</t>
-  </si>
-  <si>
-    <t>LARA</t>
-  </si>
-  <si>
     <t>TZIZIHUA</t>
   </si>
   <si>
@@ -229,34 +235,61 @@
     <t>SAID ANDRES</t>
   </si>
   <si>
+    <t>ANGEL</t>
+  </si>
+  <si>
     <t>OSVALDO</t>
   </si>
   <si>
+    <t>JOSSELIN ANDREA</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>JESUS URIEL</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>ASTRID</t>
+  </si>
+  <si>
+    <t>ITZEL ISABEL</t>
+  </si>
+  <si>
+    <t>JOSE MIGUEL</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
     <t>REYNA ARISBETH</t>
   </si>
   <si>
+    <t>ANALI</t>
+  </si>
+  <si>
     <t>DULCE FERNANDA</t>
   </si>
   <si>
-    <t>ERICK DE JESUS</t>
+    <t>AMARELY GUADALUPE</t>
   </si>
   <si>
     <t>ALEJANDRA</t>
   </si>
   <si>
-    <t>ALISSON FERNANDA</t>
-  </si>
-  <si>
-    <t>AMYRA NAHOMY</t>
-  </si>
-  <si>
-    <t>ASTRID</t>
-  </si>
-  <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
-    <t>JOSE MIGUEL</t>
+    <t>LUIS DIEGO</t>
+  </si>
+  <si>
+    <t>FATIMA</t>
+  </si>
+  <si>
+    <t>DANIELA DEL CARMEN</t>
+  </si>
+  <si>
+    <t>MARCOS</t>
   </si>
   <si>
     <t>EMMANUEL</t>
@@ -266,27 +299,6 @@
   </si>
   <si>
     <t>JUAN GUILLERMO</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
-  </si>
-  <si>
-    <t>DANIELA DEL CARMEN</t>
-  </si>
-  <si>
-    <t>MARCOS</t>
   </si>
   <si>
     <t>MICHELLE ROBERTA</t>
@@ -1157,7 +1169,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1195,10 +1207,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1218,10 +1230,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1241,10 +1253,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1264,10 +1276,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1287,10 +1299,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D6" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1304,16 +1316,16 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>20330051920070</v>
+        <v>20330051920091</v>
       </c>
       <c r="B7" t="s">
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1327,22 +1339,22 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8">
-        <v>20330051920190</v>
+        <v>20330051920070</v>
       </c>
       <c r="B8" t="s">
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D8" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8">
         <v>2</v>
@@ -1350,7 +1362,7 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>20330051920193</v>
+        <v>19330051920177</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
@@ -1359,7 +1371,7 @@
         <v>50</v>
       </c>
       <c r="D9" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1373,7 +1385,7 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920196</v>
+        <v>20330051920218</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
@@ -1382,7 +1394,7 @@
         <v>51</v>
       </c>
       <c r="D10" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1396,16 +1408,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920214</v>
+        <v>20330051920259</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>52</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1419,22 +1431,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>20330051920218</v>
+        <v>19330051920360</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D12" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E12" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1442,16 +1454,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920360</v>
+        <v>19330051920436</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="D13" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1465,16 +1477,16 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920436</v>
+        <v>19330051920393</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="D14" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="E14" t="s">
         <v>9</v>
@@ -1488,22 +1500,22 @@
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>19330051920393</v>
+        <v>20330051920317</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>22</v>
+        <v>54</v>
       </c>
       <c r="D15" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="E15" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G15">
         <v>2</v>
@@ -1511,114 +1523,114 @@
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>20330051920317</v>
+        <v>18330051920156</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>53</v>
       </c>
       <c r="D16" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920397</v>
+        <v>20330051920190</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D17" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
       </c>
       <c r="F17" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G17">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920326</v>
+        <v>20330051920191</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="D18" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
       </c>
       <c r="F18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G18">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920329</v>
+        <v>20330051920193</v>
       </c>
       <c r="B19" t="s">
         <v>36</v>
       </c>
       <c r="C19" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D19" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
       </c>
       <c r="F19" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G19">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>18330051920156</v>
+        <v>20330051920198</v>
       </c>
       <c r="B20" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C20" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="D20" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
       </c>
       <c r="F20" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G20">
         <v>1</v>
@@ -1626,16 +1638,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920191</v>
+        <v>20330051920214</v>
       </c>
       <c r="B21" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C21" t="s">
         <v>59</v>
       </c>
       <c r="D21" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1649,16 +1661,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920198</v>
+        <v>20330051920217</v>
       </c>
       <c r="B22" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="C22" t="s">
         <v>60</v>
       </c>
       <c r="D22" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1672,22 +1684,22 @@
     </row>
     <row r="23" spans="1:7">
       <c r="A23">
-        <v>20330051920217</v>
+        <v>19330051920383</v>
       </c>
       <c r="B23" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C23" t="s">
         <v>61</v>
       </c>
       <c r="D23" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G23">
         <v>1</v>
@@ -1695,22 +1707,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>19330051920383</v>
+        <v>20330051920320</v>
       </c>
       <c r="B24" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C24" t="s">
         <v>62</v>
       </c>
       <c r="D24" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E24" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F24" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1718,16 +1730,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920320</v>
+        <v>20330051920322</v>
       </c>
       <c r="B25" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>63</v>
+        <v>33</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1741,16 +1753,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920322</v>
+        <v>20330051920397</v>
       </c>
       <c r="B26" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>37</v>
+        <v>63</v>
       </c>
       <c r="D26" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1764,16 +1776,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920331</v>
+        <v>20330051920326</v>
       </c>
       <c r="B27" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
       <c r="D27" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1787,16 +1799,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920335</v>
+        <v>20330051920329</v>
       </c>
       <c r="B28" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D28" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1805,6 +1817,52 @@
         <v>13</v>
       </c>
       <c r="G28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7">
+      <c r="A29">
+        <v>20330051920331</v>
+      </c>
+      <c r="B29" t="s">
+        <v>43</v>
+      </c>
+      <c r="C29" t="s">
+        <v>55</v>
+      </c>
+      <c r="D29" t="s">
+        <v>94</v>
+      </c>
+      <c r="E29" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>13</v>
+      </c>
+      <c r="G29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7">
+      <c r="A30">
+        <v>20330051920335</v>
+      </c>
+      <c r="B30" t="s">
+        <v>44</v>
+      </c>
+      <c r="C30" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" t="s">
+        <v>8</v>
+      </c>
+      <c r="F30" t="s">
+        <v>13</v>
+      </c>
+      <c r="G30">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
+++ b/docentes/Polanco Domínguez Rosa María - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="102">
   <si>
     <t>Mat</t>
   </si>
@@ -97,42 +97,48 @@
     <t>TEXCAHUA</t>
   </si>
   <si>
+    <t>ESTEVEZ</t>
+  </si>
+  <si>
+    <t>GALVEZ</t>
+  </si>
+  <si>
+    <t>DE LA LUZ</t>
+  </si>
+  <si>
+    <t>DE LA TEJA</t>
+  </si>
+  <si>
+    <t>BRETON</t>
+  </si>
+  <si>
+    <t>FLORES</t>
+  </si>
+  <si>
+    <t>ASCENCION</t>
+  </si>
+  <si>
+    <t>ARIAS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
-    <t>DE LA TEJA</t>
-  </si>
-  <si>
     <t>XOTLANIHUA</t>
   </si>
   <si>
-    <t>BRETON</t>
+    <t>MENDEZ</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
     <t>APALE</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>ASCENCION</t>
-  </si>
-  <si>
-    <t>ARIAS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>MENDEZ</t>
-  </si>
-  <si>
     <t>CANTELLAN</t>
   </si>
   <si>
@@ -172,6 +178,15 @@
     <t>MARTINEZ</t>
   </si>
   <si>
+    <t>MORENO</t>
+  </si>
+  <si>
+    <t>COLOHUA</t>
+  </si>
+  <si>
+    <t>OLIVERA</t>
+  </si>
+  <si>
     <t>RAMIREZ</t>
   </si>
   <si>
@@ -181,9 +196,6 @@
     <t>PEREZ</t>
   </si>
   <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
     <t>CASTILLO</t>
   </si>
   <si>
@@ -241,49 +253,55 @@
     <t>OSVALDO</t>
   </si>
   <si>
+    <t>ERICK DE JESUS</t>
+  </si>
+  <si>
+    <t>ANTONIO ABIDAN</t>
+  </si>
+  <si>
+    <t>CRISTHIAN</t>
+  </si>
+  <si>
+    <t>ALISSON FERNANDA</t>
+  </si>
+  <si>
+    <t>AMYRA NAHOMY</t>
+  </si>
+  <si>
+    <t>MIGUEL ANGEL</t>
+  </si>
+  <si>
+    <t>REYNA ARISBETH</t>
+  </si>
+  <si>
+    <t>ANALI</t>
+  </si>
+  <si>
+    <t>DULCE FERNANDA</t>
+  </si>
+  <si>
+    <t>AMARELY GUADALUPE</t>
+  </si>
+  <si>
+    <t>ALEJANDRA</t>
+  </si>
+  <si>
     <t>JOSSELIN ANDREA</t>
   </si>
   <si>
-    <t>ALISSON FERNANDA</t>
+    <t>LUIS DIEGO</t>
   </si>
   <si>
     <t>JESUS URIEL</t>
   </si>
   <si>
-    <t>AMYRA NAHOMY</t>
+    <t>FATIMA</t>
   </si>
   <si>
     <t>ASTRID</t>
   </si>
   <si>
-    <t>ITZEL ISABEL</t>
-  </si>
-  <si>
     <t>JOSE MIGUEL</t>
-  </si>
-  <si>
-    <t>MIGUEL ANGEL</t>
-  </si>
-  <si>
-    <t>REYNA ARISBETH</t>
-  </si>
-  <si>
-    <t>ANALI</t>
-  </si>
-  <si>
-    <t>DULCE FERNANDA</t>
-  </si>
-  <si>
-    <t>AMARELY GUADALUPE</t>
-  </si>
-  <si>
-    <t>ALEJANDRA</t>
-  </si>
-  <si>
-    <t>LUIS DIEGO</t>
-  </si>
-  <si>
-    <t>FATIMA</t>
   </si>
   <si>
     <t>DANIELA DEL CARMEN</t>
@@ -783,19 +801,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>73.81</v>
+        <v>76.19</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -952,19 +970,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>73.81</v>
+        <v>76.19</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1121,19 +1139,19 @@
         <v>42</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>71.43000000000001</v>
+        <v>73.81</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>7.9</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1169,7 +1187,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1207,10 +1225,10 @@
         <v>20</v>
       </c>
       <c r="C2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1230,10 +1248,10 @@
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D3" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
         <v>8</v>
@@ -1253,10 +1271,10 @@
         <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D4" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="E4" t="s">
         <v>8</v>
@@ -1276,10 +1294,10 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D5" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="E5" t="s">
         <v>8</v>
@@ -1299,10 +1317,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="E6" t="s">
         <v>8</v>
@@ -1322,10 +1340,10 @@
         <v>24</v>
       </c>
       <c r="C7" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D7" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="E7" t="s">
         <v>8</v>
@@ -1345,10 +1363,10 @@
         <v>25</v>
       </c>
       <c r="C8" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D8" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="E8" t="s">
         <v>8</v>
@@ -1362,16 +1380,16 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9">
-        <v>19330051920177</v>
+        <v>20330051920196</v>
       </c>
       <c r="B9" t="s">
         <v>26</v>
       </c>
       <c r="C9" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="E9" t="s">
         <v>8</v>
@@ -1385,16 +1403,16 @@
     </row>
     <row r="10" spans="1:7">
       <c r="A10">
-        <v>20330051920218</v>
+        <v>20330051920200</v>
       </c>
       <c r="B10" t="s">
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="D10" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="E10" t="s">
         <v>8</v>
@@ -1408,16 +1426,16 @@
     </row>
     <row r="11" spans="1:7">
       <c r="A11">
-        <v>20330051920259</v>
+        <v>20330051920204</v>
       </c>
       <c r="B11" t="s">
         <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>55</v>
       </c>
       <c r="D11" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="E11" t="s">
         <v>8</v>
@@ -1431,22 +1449,22 @@
     </row>
     <row r="12" spans="1:7">
       <c r="A12">
-        <v>19330051920360</v>
+        <v>20330051920218</v>
       </c>
       <c r="B12" t="s">
         <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="D12" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="E12" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F12" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G12">
         <v>2</v>
@@ -1454,16 +1472,16 @@
     </row>
     <row r="13" spans="1:7">
       <c r="A13">
-        <v>19330051920436</v>
+        <v>19330051920360</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="D13" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="E13" t="s">
         <v>9</v>
@@ -1477,68 +1495,68 @@
     </row>
     <row r="14" spans="1:7">
       <c r="A14">
-        <v>19330051920393</v>
+        <v>18330051920156</v>
       </c>
       <c r="B14" t="s">
         <v>31</v>
       </c>
       <c r="C14" t="s">
-        <v>22</v>
+        <v>58</v>
       </c>
       <c r="D14" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="E14" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F14" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G14">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:7">
       <c r="A15">
-        <v>20330051920317</v>
+        <v>20330051920190</v>
       </c>
       <c r="B15" t="s">
         <v>32</v>
       </c>
       <c r="C15" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E15" t="s">
         <v>8</v>
       </c>
       <c r="F15" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G15">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="A16">
-        <v>18330051920156</v>
+        <v>20330051920191</v>
       </c>
       <c r="B16" t="s">
         <v>33</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="D16" t="s">
-        <v>81</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
         <v>8</v>
       </c>
       <c r="F16" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G16">
         <v>1</v>
@@ -1546,16 +1564,16 @@
     </row>
     <row r="17" spans="1:7">
       <c r="A17">
-        <v>20330051920190</v>
+        <v>20330051920193</v>
       </c>
       <c r="B17" t="s">
         <v>34</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="D17" t="s">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="E17" t="s">
         <v>8</v>
@@ -1569,16 +1587,16 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18">
-        <v>20330051920191</v>
+        <v>20330051920198</v>
       </c>
       <c r="B18" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C18" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="D18" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
         <v>8</v>
@@ -1592,16 +1610,16 @@
     </row>
     <row r="19" spans="1:7">
       <c r="A19">
-        <v>20330051920193</v>
+        <v>20330051920214</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C19" t="s">
-        <v>57</v>
+        <v>63</v>
       </c>
       <c r="D19" t="s">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="E19" t="s">
         <v>8</v>
@@ -1615,16 +1633,16 @@
     </row>
     <row r="20" spans="1:7">
       <c r="A20">
-        <v>20330051920198</v>
+        <v>19330051920177</v>
       </c>
       <c r="B20" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C20" t="s">
-        <v>58</v>
+        <v>52</v>
       </c>
       <c r="D20" t="s">
-        <v>85</v>
+        <v>89</v>
       </c>
       <c r="E20" t="s">
         <v>8</v>
@@ -1638,16 +1656,16 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21">
-        <v>20330051920214</v>
+        <v>20330051920217</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C21" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="D21" t="s">
-        <v>86</v>
+        <v>90</v>
       </c>
       <c r="E21" t="s">
         <v>8</v>
@@ -1661,16 +1679,16 @@
     </row>
     <row r="22" spans="1:7">
       <c r="A22">
-        <v>20330051920217</v>
+        <v>20330051920259</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="C22" t="s">
-        <v>60</v>
+        <v>36</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
         <v>8</v>
@@ -1690,10 +1708,10 @@
         <v>37</v>
       </c>
       <c r="C23" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="E23" t="s">
         <v>9</v>
@@ -1707,22 +1725,22 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24">
-        <v>20330051920320</v>
+        <v>19330051920436</v>
       </c>
       <c r="B24" t="s">
         <v>38</v>
       </c>
       <c r="C24" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="E24" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F24" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G24">
         <v>1</v>
@@ -1730,16 +1748,16 @@
     </row>
     <row r="25" spans="1:7">
       <c r="A25">
-        <v>20330051920322</v>
+        <v>20330051920317</v>
       </c>
       <c r="B25" t="s">
         <v>39</v>
       </c>
       <c r="C25" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="D25" t="s">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="E25" t="s">
         <v>8</v>
@@ -1753,16 +1771,16 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26">
-        <v>20330051920397</v>
+        <v>20330051920320</v>
       </c>
       <c r="B26" t="s">
         <v>40</v>
       </c>
       <c r="C26" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>95</v>
       </c>
       <c r="E26" t="s">
         <v>8</v>
@@ -1776,16 +1794,16 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27">
-        <v>20330051920326</v>
+        <v>20330051920322</v>
       </c>
       <c r="B27" t="s">
         <v>41</v>
       </c>
       <c r="C27" t="s">
-        <v>64</v>
+        <v>31</v>
       </c>
       <c r="D27" t="s">
-        <v>92</v>
+        <v>96</v>
       </c>
       <c r="E27" t="s">
         <v>8</v>
@@ -1799,16 +1817,16 @@
     </row>
     <row r="28" spans="1:7">
       <c r="A28">
-        <v>20330051920329</v>
+        <v>20330051920397</v>
       </c>
       <c r="B28" t="s">
         <v>42</v>
       </c>
       <c r="C28" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D28" t="s">
-        <v>93</v>
+        <v>97</v>
       </c>
       <c r="E28" t="s">
         <v>8</v>
@@ -1822,16 +1840,16 @@
     </row>
     <row r="29" spans="1:7">
       <c r="A29">
-        <v>20330051920331</v>
+        <v>20330051920326</v>
       </c>
       <c r="B29" t="s">
         <v>43</v>
       </c>
       <c r="C29" t="s">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="D29" t="s">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="E29" t="s">
         <v>8</v>
@@ -1845,16 +1863,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30">
-        <v>20330051920335</v>
+        <v>20330051920329</v>
       </c>
       <c r="B30" t="s">
         <v>44</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="E30" t="s">
         <v>8</v>
@@ -1863,6 +1881,52 @@
         <v>13</v>
       </c>
       <c r="G30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="A31">
+        <v>20330051920331</v>
+      </c>
+      <c r="B31" t="s">
+        <v>45</v>
+      </c>
+      <c r="C31" t="s">
+        <v>59</v>
+      </c>
+      <c r="D31" t="s">
+        <v>100</v>
+      </c>
+      <c r="E31" t="s">
+        <v>8</v>
+      </c>
+      <c r="F31" t="s">
+        <v>13</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7">
+      <c r="A32">
+        <v>20330051920335</v>
+      </c>
+      <c r="B32" t="s">
+        <v>46</v>
+      </c>
+      <c r="C32" t="s">
+        <v>70</v>
+      </c>
+      <c r="D32" t="s">
+        <v>101</v>
+      </c>
+      <c r="E32" t="s">
+        <v>8</v>
+      </c>
+      <c r="F32" t="s">
+        <v>13</v>
+      </c>
+      <c r="G32">
         <v>1</v>
       </c>
     </row>
